--- a/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
+++ b/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supi\source\repos\IfcManager\IfcManager.BL\Files\IfcManagerFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8A0851-9B7A-4F36-A0A7-F0197E94E56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C27F49-7F58-49E4-A1D1-855DE69F1C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6105" yWindow="2490" windowWidth="21600" windowHeight="12645" tabRatio="745" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24105" yWindow="4080" windowWidth="30870" windowHeight="15345" tabRatio="745" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7230" uniqueCount="4527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7235" uniqueCount="4528">
   <si>
     <t>Data Type</t>
   </si>
@@ -13496,66 +13496,9 @@
     <t>PropertySet_3L_4D</t>
   </si>
   <si>
-    <t>TN-IMT</t>
-  </si>
-  <si>
-    <t>TN-CTC-N</t>
-  </si>
-  <si>
-    <t>TN-CTC-S</t>
-  </si>
-  <si>
-    <t>TN-RAMP-N</t>
-  </si>
-  <si>
-    <t>TN-RAMP-S</t>
-  </si>
-  <si>
-    <t>EL01-W</t>
-  </si>
-  <si>
-    <t>EL01-E</t>
-  </si>
-  <si>
-    <t>EL02-W</t>
-  </si>
-  <si>
-    <t>EL02-E</t>
-  </si>
-  <si>
-    <t>EL03-W</t>
-  </si>
-  <si>
-    <t>EL03-E</t>
-  </si>
-  <si>
-    <t>EL04-W</t>
-  </si>
-  <si>
-    <t>EL04-E</t>
-  </si>
-  <si>
-    <t>EL05-W</t>
-  </si>
-  <si>
-    <t>EL05-E</t>
-  </si>
-  <si>
-    <t>EL06-W</t>
-  </si>
-  <si>
-    <t>EL06-E</t>
-  </si>
-  <si>
     <t>4DGroup</t>
   </si>
   <si>
-    <t>Project phase</t>
-  </si>
-  <si>
-    <t>Traffic stage</t>
-  </si>
-  <si>
     <t>&lt;ConstructionPhase&gt;.&lt;WBSID&gt;.&lt;TypeID&gt;.&lt;WorkStep&gt;</t>
   </si>
   <si>
@@ -13623,6 +13566,66 @@
   </si>
   <si>
     <t>STR_NOISE_BARRIER</t>
+  </si>
+  <si>
+    <t>Pilot</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>TN-CP-N</t>
+  </si>
+  <si>
+    <t>TN-CP-S</t>
+  </si>
+  <si>
+    <t>IMT-EL01-W</t>
+  </si>
+  <si>
+    <t>IMT-EL01-E</t>
+  </si>
+  <si>
+    <t>IMT-EL02-W</t>
+  </si>
+  <si>
+    <t>IMT-EL02-E</t>
+  </si>
+  <si>
+    <t>IMT-EL03-W</t>
+  </si>
+  <si>
+    <t>IMT-EL03-E</t>
+  </si>
+  <si>
+    <t>IMT-EL04-W</t>
+  </si>
+  <si>
+    <t>IMT-EL04-E</t>
+  </si>
+  <si>
+    <t>IMT-EL05-W</t>
+  </si>
+  <si>
+    <t>IMT-EL05-E</t>
+  </si>
+  <si>
+    <t>IMT-EL06-W</t>
+  </si>
+  <si>
+    <t>IMT-EL06-E</t>
+  </si>
+  <si>
+    <t>CTC-N</t>
+  </si>
+  <si>
+    <t>CTC-S</t>
+  </si>
+  <si>
+    <t>RAMP-N</t>
+  </si>
+  <si>
+    <t>RAMP-S</t>
   </si>
 </sst>
 </file>
@@ -13712,7 +13715,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -13746,6 +13749,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -13854,7 +13862,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
@@ -13895,11 +13903,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14127,8 +14135,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B59" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:B59" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B56" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:B56" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="6" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="5" dataCellStyle="Normal 2"/>
@@ -14570,7 +14578,7 @@
         <v>4483</v>
       </c>
       <c r="B12" t="s">
-        <v>4501</v>
+        <v>4484</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -14712,7 +14720,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4524</v>
+        <v>4505</v>
       </c>
       <c r="B2" t="s">
         <v>159</v>
@@ -14736,10 +14744,10 @@
         <v>358</v>
       </c>
       <c r="I2" t="s">
-        <v>4502</v>
+        <v>4508</v>
       </c>
       <c r="J2" t="s">
-        <v>4507</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -14767,11 +14775,8 @@
       <c r="H3" t="s">
         <v>359</v>
       </c>
-      <c r="I3" t="s">
-        <v>4503</v>
-      </c>
       <c r="J3" t="s">
-        <v>4509</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -14800,7 +14805,7 @@
         <v>360</v>
       </c>
       <c r="J4" t="s">
-        <v>4508</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -14877,7 +14882,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>151</v>
@@ -14894,7 +14899,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>152</v>
@@ -14911,7 +14916,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>153</v>
@@ -14928,7 +14933,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>4463</v>
@@ -14945,7 +14950,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>4464</v>
@@ -14962,7 +14967,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>4465</v>
@@ -14979,7 +14984,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>4466</v>
@@ -14996,7 +15001,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>4467</v>
@@ -15013,7 +15018,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>4468</v>
@@ -15030,7 +15035,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>4469</v>
@@ -15044,7 +15049,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
         <v>4470</v>
@@ -15058,7 +15063,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
         <v>4471</v>
@@ -15072,7 +15077,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>4472</v>
@@ -15086,7 +15091,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>4473</v>
@@ -15097,7 +15102,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
         <v>4474</v>
@@ -15108,7 +15113,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
         <v>4475</v>
@@ -15119,7 +15124,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>4476</v>
@@ -15130,7 +15135,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
         <v>4477</v>
@@ -15141,10 +15146,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>4489</v>
+        <v>4512</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>184</v>
@@ -15152,10 +15157,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>4490</v>
+        <v>4513</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>185</v>
@@ -15163,10 +15168,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>4491</v>
+        <v>4514</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>186</v>
@@ -15174,10 +15179,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>4492</v>
+        <v>4515</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>187</v>
@@ -15185,10 +15190,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>4493</v>
+        <v>4516</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>188</v>
@@ -15196,10 +15201,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>4494</v>
+        <v>4517</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>189</v>
@@ -15207,10 +15212,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>4495</v>
+        <v>4518</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>190</v>
@@ -15218,10 +15223,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>4496</v>
+        <v>4519</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>191</v>
@@ -15229,10 +15234,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>4497</v>
+        <v>4520</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>192</v>
@@ -15240,10 +15245,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>4498</v>
+        <v>4521</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>193</v>
@@ -15251,10 +15256,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>4499</v>
+        <v>4522</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>194</v>
@@ -15262,10 +15267,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>4500</v>
+        <v>4523</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>195</v>
@@ -15273,7 +15278,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4524</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>196</v>
@@ -15281,7 +15289,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4525</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>197</v>
@@ -15289,7 +15300,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4526</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>198</v>
@@ -15297,7 +15311,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4527</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>199</v>
@@ -15305,7 +15322,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>200</v>
@@ -15313,7 +15330,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>201</v>
@@ -15321,7 +15338,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>202</v>
@@ -15329,7 +15346,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>203</v>
@@ -15337,7 +15354,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>204</v>
@@ -15345,7 +15362,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>205</v>
@@ -15353,7 +15370,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>206</v>
@@ -15361,7 +15378,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>207</v>
@@ -15369,7 +15386,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>208</v>
@@ -15377,7 +15394,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>209</v>
@@ -15385,7 +15402,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>210</v>
@@ -15393,7 +15410,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>211</v>
@@ -15401,7 +15418,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>212</v>
@@ -15409,7 +15426,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>213</v>
@@ -15417,7 +15434,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>214</v>
@@ -15425,7 +15442,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>215</v>
@@ -15433,7 +15450,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>216</v>
@@ -15441,7 +15458,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>217</v>
@@ -15449,7 +15466,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>219</v>
@@ -15457,7 +15474,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>220</v>
@@ -15465,7 +15482,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>221</v>
@@ -15473,7 +15490,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>222</v>
@@ -15481,7 +15498,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>219</v>
@@ -15489,7 +15506,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>220</v>
@@ -15497,7 +15514,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>221</v>
@@ -15505,7 +15522,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>222</v>
@@ -15513,7 +15530,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>223</v>
@@ -15521,7 +15538,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>224</v>
@@ -15529,7 +15546,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>225</v>
@@ -15537,7 +15554,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>226</v>
@@ -15545,7 +15562,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>227</v>
@@ -15553,7 +15570,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>228</v>
@@ -15561,7 +15578,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>229</v>
@@ -15569,7 +15586,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>230</v>
@@ -15577,7 +15594,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>231</v>
@@ -15585,7 +15602,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>232</v>
@@ -15593,7 +15610,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>233</v>
@@ -15601,7 +15618,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>234</v>
@@ -15609,7 +15626,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>235</v>
@@ -15617,7 +15634,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>236</v>
@@ -15625,7 +15642,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>237</v>
@@ -15633,7 +15650,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>238</v>
@@ -15641,7 +15658,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>239</v>
@@ -15649,7 +15666,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>240</v>
@@ -15657,7 +15674,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>241</v>
@@ -15665,7 +15682,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>242</v>
@@ -15673,7 +15690,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>244</v>
@@ -15681,7 +15698,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>245</v>
@@ -15689,7 +15706,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>246</v>
@@ -15697,7 +15714,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>247</v>
@@ -15705,7 +15722,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>248</v>
@@ -15713,7 +15730,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>249</v>
@@ -15721,7 +15738,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>250</v>
@@ -15729,7 +15746,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>252</v>
@@ -15737,7 +15754,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>253</v>
@@ -15745,7 +15762,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>254</v>
@@ -15753,7 +15770,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>255</v>
@@ -15761,7 +15778,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>256</v>
@@ -15769,7 +15786,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>257</v>
@@ -15777,7 +15794,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>258</v>
@@ -15785,7 +15802,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>259</v>
@@ -15793,7 +15810,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>260</v>
@@ -15801,7 +15818,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>261</v>
@@ -15809,7 +15826,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>263</v>
@@ -15817,7 +15834,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>121</v>
+        <v>4509</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>264</v>
@@ -15825,7 +15842,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>265</v>
@@ -15833,7 +15850,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>266</v>
@@ -15841,7 +15858,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>267</v>
@@ -15849,7 +15866,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>125</v>
+        <v>4510</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>268</v>
@@ -15857,7 +15874,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>4484</v>
+        <v>4511</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>269</v>
@@ -15865,7 +15882,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>4485</v>
+        <v>129</v>
       </c>
       <c r="D112" s="10" t="s">
         <v>271</v>
@@ -15873,7 +15890,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>4486</v>
+        <v>130</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>272</v>
@@ -15881,7 +15898,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>4487</v>
+        <v>131</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>273</v>
@@ -15889,7 +15906,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>4488</v>
+        <v>132</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>274</v>
@@ -15897,7 +15914,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>275</v>
@@ -15905,7 +15922,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>276</v>
@@ -15913,7 +15930,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>277</v>
@@ -15921,7 +15938,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>279</v>
@@ -15929,7 +15946,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>280</v>
@@ -15937,7 +15954,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>281</v>
@@ -15945,7 +15962,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>282</v>
@@ -15953,7 +15970,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>283</v>
@@ -15961,7 +15978,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>285</v>
@@ -15969,7 +15986,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D125" s="10" t="s">
         <v>286</v>
@@ -15977,7 +15994,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>287</v>
@@ -15985,7 +16002,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>288</v>
@@ -15993,106 +16010,88 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>140</v>
-      </c>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D129" s="10" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>141</v>
-      </c>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D130" s="10" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>142</v>
-      </c>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D131" s="10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>143</v>
-      </c>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D132" s="10" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>144</v>
-      </c>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D133" s="10" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>145</v>
-      </c>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D134" s="10" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D135" s="10" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D136" s="10" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D137" s="10" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D138" s="10" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D139" s="10" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D140" s="10" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D141" s="10" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D142" s="10" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D143" s="10" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D144" s="10" t="s">
         <v>305</v>
       </c>
@@ -16203,8 +16202,8 @@
       </c>
     </row>
     <row r="166" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D166" s="24" t="s">
-        <v>4525</v>
+      <c r="D166" s="10" t="s">
+        <v>4506</v>
       </c>
     </row>
   </sheetData>
@@ -39716,7 +39715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6089D82B-CC96-4176-9A54-02325BF7F952}">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -39732,440 +39731,444 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>4524</v>
+      <c r="A2" s="23" t="s">
+        <v>4505</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="10" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="10" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="10" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="10" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="10" t="s">
         <v>4463</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="10" t="s">
         <v>4464</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="10" t="s">
         <v>4465</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="10" t="s">
         <v>4466</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="10" t="s">
         <v>4467</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="10" t="s">
         <v>4468</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="10" t="s">
         <v>4469</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>4470</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="10" t="s">
         <v>4471</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="10" t="s">
         <v>4472</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="10" t="s">
         <v>4473</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="10" t="s">
         <v>4474</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="10" t="s">
         <v>4475</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="10" t="s">
         <v>4476</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="10" t="s">
         <v>4477</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="10" t="s">
         <v>4470</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="10" t="s">
         <v>4471</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="10" t="s">
         <v>4472</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="10" t="s">
         <v>4473</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="10" t="s">
         <v>4474</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="10" t="s">
         <v>4475</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="10" t="s">
         <v>4476</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="10" t="s">
         <v>4477</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>4489</v>
+      <c r="A41" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>4512</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>4490</v>
+      <c r="A42" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>4513</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>4491</v>
+      <c r="A43" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>4514</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>4492</v>
+      <c r="A44" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>4515</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>4493</v>
+      <c r="A45" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>4516</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>4494</v>
+      <c r="A46" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>4517</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>4495</v>
+      <c r="A47" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>4518</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>4496</v>
+      <c r="A48" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>4519</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>4497</v>
+      <c r="A49" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>4520</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>4498</v>
+      <c r="A50" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>4521</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>4499</v>
+      <c r="A51" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>4522</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>4484</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>4500</v>
+      <c r="A52" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B52" s="24" t="s">
+        <v>4523</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="6"/>
+      <c r="A53" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>4524</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="6"/>
+      <c r="A54" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>4525</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="6"/>
+      <c r="A55" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>4526</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="6"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="6"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="6"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="6"/>
+      <c r="A56" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>4527</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40189,7 +40192,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>4501</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -40197,7 +40200,7 @@
         <v>160</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -40205,7 +40208,7 @@
         <v>161</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -40213,7 +40216,7 @@
         <v>162</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -40221,7 +40224,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -40229,7 +40232,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -40237,7 +40240,7 @@
         <v>165</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -40245,7 +40248,7 @@
         <v>166</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -40253,7 +40256,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -40261,7 +40264,7 @@
         <v>168</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -40269,7 +40272,7 @@
         <v>169</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -40277,7 +40280,7 @@
         <v>170</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>4512</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -40285,7 +40288,7 @@
         <v>171</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>4513</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -40293,7 +40296,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>4514</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -40301,7 +40304,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>4513</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -40309,7 +40312,7 @@
         <v>174</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>4514</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -40317,7 +40320,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>4514</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -40325,7 +40328,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>4514</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -40333,7 +40336,7 @@
         <v>177</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -40341,7 +40344,7 @@
         <v>178</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -40349,7 +40352,7 @@
         <v>179</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>4513</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -40357,7 +40360,7 @@
         <v>180</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -40365,7 +40368,7 @@
         <v>181</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -40373,7 +40376,7 @@
         <v>182</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -40381,7 +40384,7 @@
         <v>183</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>4514</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -40389,7 +40392,7 @@
         <v>184</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -40397,7 +40400,7 @@
         <v>185</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -40405,7 +40408,7 @@
         <v>186</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -40413,7 +40416,7 @@
         <v>187</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>4515</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -40453,7 +40456,7 @@
         <v>192</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>4516</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -40477,7 +40480,7 @@
         <v>195</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>4517</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -40485,7 +40488,7 @@
         <v>196</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>4517</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -40493,7 +40496,7 @@
         <v>197</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>4518</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -40501,7 +40504,7 @@
         <v>198</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>4518</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -40509,7 +40512,7 @@
         <v>199</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>4518</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -40517,7 +40520,7 @@
         <v>200</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>4518</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -40525,7 +40528,7 @@
         <v>201</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>4519</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -40533,7 +40536,7 @@
         <v>202</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>4520</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -40541,7 +40544,7 @@
         <v>203</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>4520</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -40549,7 +40552,7 @@
         <v>204</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -40557,7 +40560,7 @@
         <v>205</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -40565,7 +40568,7 @@
         <v>206</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -40573,7 +40576,7 @@
         <v>207</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -40581,7 +40584,7 @@
         <v>208</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -40589,7 +40592,7 @@
         <v>209</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -40597,7 +40600,7 @@
         <v>210</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -40605,7 +40608,7 @@
         <v>211</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -40613,7 +40616,7 @@
         <v>212</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -40621,7 +40624,7 @@
         <v>213</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -40629,7 +40632,7 @@
         <v>214</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -40637,7 +40640,7 @@
         <v>215</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -40645,7 +40648,7 @@
         <v>216</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -40653,7 +40656,7 @@
         <v>217</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>4521</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -41077,7 +41080,7 @@
         <v>271</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -41085,7 +41088,7 @@
         <v>272</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -41093,7 +41096,7 @@
         <v>273</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -41101,7 +41104,7 @@
         <v>274</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -41109,7 +41112,7 @@
         <v>275</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -41117,7 +41120,7 @@
         <v>276</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -41125,7 +41128,7 @@
         <v>277</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -41133,7 +41136,7 @@
         <v>279</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -41141,7 +41144,7 @@
         <v>280</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -41149,7 +41152,7 @@
         <v>281</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -41157,7 +41160,7 @@
         <v>282</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -41165,7 +41168,7 @@
         <v>283</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>4522</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -41173,7 +41176,7 @@
         <v>285</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -41181,7 +41184,7 @@
         <v>286</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -41189,7 +41192,7 @@
         <v>287</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -41197,7 +41200,7 @@
         <v>288</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -41205,7 +41208,7 @@
         <v>289</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -41213,7 +41216,7 @@
         <v>290</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -41221,7 +41224,7 @@
         <v>291</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -41229,7 +41232,7 @@
         <v>292</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -41237,7 +41240,7 @@
         <v>293</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -41245,7 +41248,7 @@
         <v>294</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -41253,7 +41256,7 @@
         <v>295</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -41261,7 +41264,7 @@
         <v>296</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -41269,7 +41272,7 @@
         <v>297</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -41277,7 +41280,7 @@
         <v>298</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -41285,7 +41288,7 @@
         <v>299</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -41293,7 +41296,7 @@
         <v>300</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -41301,7 +41304,7 @@
         <v>301</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -41309,7 +41312,7 @@
         <v>302</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -41317,7 +41320,7 @@
         <v>303</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -41325,7 +41328,7 @@
         <v>304</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -41333,7 +41336,7 @@
         <v>306</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -41341,7 +41344,7 @@
         <v>307</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -41349,7 +41352,7 @@
         <v>308</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>4523</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -41497,11 +41500,11 @@
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="25" t="s">
-        <v>4525</v>
-      </c>
-      <c r="B165" s="26" t="s">
-        <v>4526</v>
+      <c r="A165" s="22" t="s">
+        <v>4506</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>4507</v>
       </c>
     </row>
   </sheetData>
@@ -41534,7 +41537,7 @@
         <v>4480</v>
       </c>
       <c r="D1" t="s">
-        <v>4510</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -41556,7 +41559,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>4511</v>
+        <v>4492</v>
       </c>
       <c r="D3" t="s">
         <v>348</v>
@@ -41581,10 +41584,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4505</v>
+        <v>4486</v>
       </c>
       <c r="B1" t="s">
-        <v>4506</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -41592,7 +41595,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>4504</v>
+        <v>4485</v>
       </c>
     </row>
   </sheetData>

--- a/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
+++ b/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supi\source\repos\IfcManager\IfcManager.BL\Files\IfcManagerFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C27F49-7F58-49E4-A1D1-855DE69F1C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B28E61C-C1D1-46E7-BCBB-62AACAB9941E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24105" yWindow="4080" windowWidth="30870" windowHeight="15345" tabRatio="745" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" tabRatio="745" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7235" uniqueCount="4528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7252" uniqueCount="4529">
   <si>
     <t>Data Type</t>
   </si>
@@ -13626,19 +13626,28 @@
   </si>
   <si>
     <t>RAMP-S</t>
+  </si>
+  <si>
+    <t>TUN.BAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -13757,7 +13766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -13852,70 +13861,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FC528EF5-A6D0-4D13-9CE0-C50A2E61FD77}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{F3E263F6-78E8-4EA9-B859-F8D98F8BCA78}"/>
     <cellStyle name="Normal 3 2" xfId="5" xr:uid="{562A2998-00A4-431C-A5FE-06CC06040494}"/>
+    <cellStyle name="Normal 3 3" xfId="7" xr:uid="{94348558-55DC-4749-BCAB-781F42D46C86}"/>
     <cellStyle name="Normal 4" xfId="3" xr:uid="{4F4329F8-E4C2-4E19-BD86-CB810AFB9FBE}"/>
     <cellStyle name="Normal 4 2" xfId="6" xr:uid="{C1DA66DB-F815-47B4-BB2B-3901B21386C2}"/>
+    <cellStyle name="Normal 4 3" xfId="8" xr:uid="{647E405E-89F1-46B3-9D0F-7CADBB992D37}"/>
     <cellStyle name="Normal 5" xfId="4" xr:uid="{6DF54FAE-2483-4EEF-8D6C-A9E4680CE2F0}"/>
   </cellStyles>
   <dxfs count="9">
@@ -14116,8 +14143,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:J166" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:J166" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:J167" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A1:J167" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{7CD8FD0B-335F-4B2A-AB69-8C9EE375AC9F}" name="LocationRoot"/>
     <tableColumn id="2" xr3:uid="{E22D17F3-0FB5-4869-9840-DEB0FECC3DC6}" name="SubLocation"/>
@@ -14135,8 +14162,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B56" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:B56" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B63" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:B63" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="6" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="5" dataCellStyle="Normal 2"/>
@@ -14146,8 +14173,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B165" totalsRowShown="0" tableBorderDxfId="4">
-  <autoFilter ref="A1:B165" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B166" totalsRowShown="0" tableBorderDxfId="4">
+  <autoFilter ref="A1:B166" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="3" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="2" dataCellStyle="Normal 2"/>
@@ -14671,7 +14698,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E22C3A-731E-4720-A4F4-B02EE915C838}">
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -16204,6 +16231,11 @@
     <row r="166" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D166" s="10" t="s">
         <v>4506</v>
+      </c>
+    </row>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D167" s="10" t="s">
+        <v>4528</v>
       </c>
     </row>
   </sheetData>
@@ -39715,7 +39747,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6089D82B-CC96-4176-9A54-02325BF7F952}">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -39788,10 +39820,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>152</v>
+        <v>126</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -39799,23 +39831,23 @@
         <v>140</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -39823,7 +39855,7 @@
         <v>127</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -39831,7 +39863,7 @@
         <v>127</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -39839,47 +39871,47 @@
         <v>127</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>4463</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>4464</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>4465</v>
+        <v>139</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -39887,7 +39919,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>4466</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -39895,7 +39927,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>4467</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -39903,7 +39935,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>4468</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -39911,39 +39943,39 @@
         <v>29</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>4469</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>4470</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>4471</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>4472</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>4473</v>
+        <v>29</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -39951,7 +39983,7 @@
         <v>115</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>4474</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -39959,7 +39991,7 @@
         <v>115</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>4475</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -39967,7 +39999,7 @@
         <v>115</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>4476</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -39975,47 +40007,47 @@
         <v>115</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>4477</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>4470</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>4471</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>4472</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>4473</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>4474</v>
+        <v>115</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -40023,7 +40055,7 @@
         <v>116</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>4475</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -40031,7 +40063,7 @@
         <v>116</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>4476</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -40039,55 +40071,55 @@
         <v>116</v>
       </c>
       <c r="B40" s="10" t="s">
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>4473</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>4477</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
-        <v>4509</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>4512</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
-        <v>4509</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>4513</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="24" t="s">
-        <v>4509</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>4514</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
-        <v>4509</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>4515</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="24" t="s">
-        <v>4509</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>4516</v>
-      </c>
-    </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
-        <v>4509</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>4517</v>
+      <c r="A46" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -40095,7 +40127,7 @@
         <v>4509</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>4518</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -40103,7 +40135,7 @@
         <v>4509</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>4519</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -40111,7 +40143,7 @@
         <v>4509</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>4520</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -40119,7 +40151,7 @@
         <v>4509</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>4521</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -40127,7 +40159,7 @@
         <v>4509</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>4522</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -40135,7 +40167,7 @@
         <v>4509</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>4523</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -40143,7 +40175,7 @@
         <v>4509</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>4524</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -40151,7 +40183,7 @@
         <v>4509</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>4525</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -40159,7 +40191,7 @@
         <v>4509</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>4526</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -40167,7 +40199,63 @@
         <v>4509</v>
       </c>
       <c r="B56" s="24" t="s">
+        <v>4521</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>4522</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="24" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B62" s="24" t="s">
         <v>4527</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="22" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -40180,7 +40268,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5D69-D337-4E34-A409-23B0595B8838}">
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -40724,368 +40812,368 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>223</v>
+      <c r="A68" s="10" t="s">
+        <v>4528</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>4528</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>4503</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>4503</v>
@@ -41093,7 +41181,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>4503</v>
@@ -41101,7 +41189,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>4503</v>
@@ -41109,7 +41197,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>4503</v>
@@ -41117,7 +41205,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>4503</v>
@@ -41125,7 +41213,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>4503</v>
@@ -41133,7 +41221,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>4503</v>
@@ -41141,7 +41229,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>4503</v>
@@ -41149,7 +41237,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>4503</v>
@@ -41157,7 +41245,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>4503</v>
@@ -41165,7 +41253,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>4503</v>
@@ -41173,15 +41261,15 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>4504</v>
@@ -41189,7 +41277,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>4504</v>
@@ -41197,7 +41285,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>4504</v>
@@ -41205,7 +41293,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>4504</v>
@@ -41213,7 +41301,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>4504</v>
@@ -41221,7 +41309,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>4504</v>
@@ -41229,7 +41317,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>4504</v>
@@ -41237,7 +41325,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>4504</v>
@@ -41245,7 +41333,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>4504</v>
@@ -41253,7 +41341,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>4504</v>
@@ -41261,7 +41349,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>4504</v>
@@ -41269,7 +41357,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>4504</v>
@@ -41277,7 +41365,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>4504</v>
@@ -41285,7 +41373,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>4504</v>
@@ -41293,7 +41381,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>4504</v>
@@ -41301,7 +41389,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>4504</v>
@@ -41309,7 +41397,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>4504</v>
@@ -41317,7 +41405,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>4504</v>
@@ -41325,7 +41413,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>4504</v>
@@ -41333,7 +41421,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>4504</v>
@@ -41341,7 +41429,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>4504</v>
@@ -41349,7 +41437,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>4504</v>
@@ -41357,153 +41445,161 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>310</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B164" s="6" t="s">
+      <c r="B165" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="22" t="s">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="22" t="s">
         <v>4506</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B166" s="10" t="s">
         <v>4507</v>
       </c>
     </row>

--- a/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
+++ b/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supi\source\repos\IfcManager\IfcManager.BL\Files\IfcManagerFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B28E61C-C1D1-46E7-BCBB-62AACAB9941E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51D1D39-F11D-47CB-ADBC-830A89270BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" tabRatio="745" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30330" yWindow="1935" windowWidth="19455" windowHeight="15345" tabRatio="745" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
     <sheet name="Picklist" sheetId="2" r:id="rId2"/>
-    <sheet name="Microstation Layers Mapping" sheetId="3" r:id="rId3"/>
+    <sheet name="Layers Mapping" sheetId="3" r:id="rId3"/>
     <sheet name="LocationRoot Match" sheetId="4" r:id="rId4"/>
     <sheet name="4DGroup Exact Match" sheetId="7" r:id="rId5"/>
     <sheet name="Expressions" sheetId="5" r:id="rId6"/>

--- a/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
+++ b/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supi\source\repos\IfcManager\IfcManager.BL\Files\IfcManagerFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51D1D39-F11D-47CB-ADBC-830A89270BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800E70F0-B0A2-455C-94B6-CFD62C3DC323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30330" yWindow="1935" windowWidth="19455" windowHeight="15345" tabRatio="745" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="745" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7252" uniqueCount="4529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7466" uniqueCount="4735">
   <si>
     <t>Data Type</t>
   </si>
@@ -13629,6 +13629,624 @@
   </si>
   <si>
     <t>TUN.BAL</t>
+  </si>
+  <si>
+    <t>M&amp;E component ID</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>BFD</t>
+  </si>
+  <si>
+    <t>BFI</t>
+  </si>
+  <si>
+    <t>BH</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>BRO</t>
+  </si>
+  <si>
+    <t>BPB</t>
+  </si>
+  <si>
+    <t>BT</t>
+  </si>
+  <si>
+    <t>CSA</t>
+  </si>
+  <si>
+    <t>CSK</t>
+  </si>
+  <si>
+    <t>CSR</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>DBK</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>DKO</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>DSW</t>
+  </si>
+  <si>
+    <t>DU</t>
+  </si>
+  <si>
+    <t>DYS</t>
+  </si>
+  <si>
+    <t>EBH</t>
+  </si>
+  <si>
+    <t>AFT</t>
+  </si>
+  <si>
+    <t>EEL</t>
+  </si>
+  <si>
+    <t>EFF</t>
+  </si>
+  <si>
+    <t>EGE</t>
+  </si>
+  <si>
+    <t>EIO</t>
+  </si>
+  <si>
+    <t>EKL</t>
+  </si>
+  <si>
+    <t>EKO</t>
+  </si>
+  <si>
+    <t>ELT</t>
+  </si>
+  <si>
+    <t>ENT</t>
+  </si>
+  <si>
+    <t>EVA</t>
+  </si>
+  <si>
+    <t>EVB</t>
+  </si>
+  <si>
+    <t>FKO</t>
+  </si>
+  <si>
+    <t>FLB</t>
+  </si>
+  <si>
+    <t>FLV</t>
+  </si>
+  <si>
+    <t>FLH</t>
+  </si>
+  <si>
+    <t>FLI</t>
+  </si>
+  <si>
+    <t>FLN</t>
+  </si>
+  <si>
+    <t>FLU</t>
+  </si>
+  <si>
+    <t>FO</t>
+  </si>
+  <si>
+    <t>FOB</t>
+  </si>
+  <si>
+    <t>FS</t>
+  </si>
+  <si>
+    <t>FIK</t>
+  </si>
+  <si>
+    <t>FTB</t>
+  </si>
+  <si>
+    <t>GAM</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>HAI</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>HAU</t>
+  </si>
+  <si>
+    <t>HO</t>
+  </si>
+  <si>
+    <t>HPA</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>IDA</t>
+  </si>
+  <si>
+    <t>INC</t>
+  </si>
+  <si>
+    <t>IKF</t>
+  </si>
+  <si>
+    <t>IKV</t>
+  </si>
+  <si>
+    <t>IOM</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>KFV</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>KL</t>
+  </si>
+  <si>
+    <t>KFC</t>
+  </si>
+  <si>
+    <t>KNV</t>
+  </si>
+  <si>
+    <t>KOV</t>
+  </si>
+  <si>
+    <t>LSS</t>
+  </si>
+  <si>
+    <t>LEV</t>
+  </si>
+  <si>
+    <t>LIND</t>
+  </si>
+  <si>
+    <t>LGEN</t>
+  </si>
+  <si>
+    <t>LUD</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>LSP</t>
+  </si>
+  <si>
+    <t>LUX</t>
+  </si>
+  <si>
+    <t>MAB</t>
+  </si>
+  <si>
+    <t>MAF</t>
+  </si>
+  <si>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>MAK</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>MAV</t>
+  </si>
+  <si>
+    <t>MBA</t>
+  </si>
+  <si>
+    <t>MEC</t>
+  </si>
+  <si>
+    <t>MIC</t>
+  </si>
+  <si>
+    <t>MST</t>
+  </si>
+  <si>
+    <t>MVB</t>
+  </si>
+  <si>
+    <t>MVK</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>NEB</t>
+  </si>
+  <si>
+    <t>NEH</t>
+  </si>
+  <si>
+    <t>NEL</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>NOX</t>
+  </si>
+  <si>
+    <t>NVA</t>
+  </si>
+  <si>
+    <t>OKA</t>
+  </si>
+  <si>
+    <t>OPS</t>
+  </si>
+  <si>
+    <t>PBH</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>PDV</t>
+  </si>
+  <si>
+    <t>PFI</t>
+  </si>
+  <si>
+    <t>PFU</t>
+  </si>
+  <si>
+    <t>PGE</t>
+  </si>
+  <si>
+    <t>PIR</t>
+  </si>
+  <si>
+    <t>PKB</t>
+  </si>
+  <si>
+    <t>PKL</t>
+  </si>
+  <si>
+    <t>PKO</t>
+  </si>
+  <si>
+    <t>POD</t>
+  </si>
+  <si>
+    <t>POV</t>
+  </si>
+  <si>
+    <t>POW</t>
+  </si>
+  <si>
+    <t>POA</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>PRT</t>
+  </si>
+  <si>
+    <t>PSV</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>PUA</t>
+  </si>
+  <si>
+    <t>RAA</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>PTI</t>
+  </si>
+  <si>
+    <t>PTU</t>
+  </si>
+  <si>
+    <t>PU</t>
+  </si>
+  <si>
+    <t>PVA</t>
+  </si>
+  <si>
+    <t>PVT</t>
+  </si>
+  <si>
+    <t>PVB</t>
+  </si>
+  <si>
+    <t>PVI</t>
+  </si>
+  <si>
+    <t>PVU</t>
+  </si>
+  <si>
+    <t>RAD</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>REC</t>
+  </si>
+  <si>
+    <t>ROV</t>
+  </si>
+  <si>
+    <t>ROG</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>SIC</t>
+  </si>
+  <si>
+    <t>SIV</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>SKO</t>
+  </si>
+  <si>
+    <t>SNS</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>SMG</t>
+  </si>
+  <si>
+    <t>SMI</t>
+  </si>
+  <si>
+    <t>SMP</t>
+  </si>
+  <si>
+    <t>SMR</t>
+  </si>
+  <si>
+    <t>SMU</t>
+  </si>
+  <si>
+    <t>SOS</t>
+  </si>
+  <si>
+    <t>SPB</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>STA</t>
+  </si>
+  <si>
+    <t>STO</t>
+  </si>
+  <si>
+    <t>SVR</t>
+  </si>
+  <si>
+    <t>TBE</t>
+  </si>
+  <si>
+    <t>TBI</t>
+  </si>
+  <si>
+    <t>TBU</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>TDP</t>
+  </si>
+  <si>
+    <t>TDF</t>
+  </si>
+  <si>
+    <t>TEG</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+  <si>
+    <t>TFG</t>
+  </si>
+  <si>
+    <t>TFI</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>TKA</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>TND</t>
+  </si>
+  <si>
+    <t>TRU</t>
+  </si>
+  <si>
+    <t>TRD</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>TU</t>
+  </si>
+  <si>
+    <t>TUD</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>VAC</t>
+  </si>
+  <si>
+    <t>VAE</t>
+  </si>
+  <si>
+    <t>VAR</t>
+  </si>
+  <si>
+    <t>VAV</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>VBX</t>
+  </si>
+  <si>
+    <t>VD</t>
+  </si>
+  <si>
+    <t>VE</t>
+  </si>
+  <si>
+    <t>VEI</t>
+  </si>
+  <si>
+    <t>VER</t>
+  </si>
+  <si>
+    <t>VEU</t>
+  </si>
+  <si>
+    <t>VFI</t>
+  </si>
+  <si>
+    <t>VIK</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
+    <t>VIM</t>
+  </si>
+  <si>
+    <t>VK</t>
+  </si>
+  <si>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>VMO</t>
+  </si>
+  <si>
+    <t>VS</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t>VT1</t>
+  </si>
+  <si>
+    <t>VT2</t>
+  </si>
+  <si>
+    <t>VIH</t>
+  </si>
+  <si>
+    <t>VIR</t>
+  </si>
+  <si>
+    <t>VMS</t>
+  </si>
+  <si>
+    <t>VOT</t>
+  </si>
+  <si>
+    <t>VSLS</t>
+  </si>
+  <si>
+    <t>VUR</t>
+  </si>
+  <si>
+    <t>VVF</t>
+  </si>
+  <si>
+    <t>VVX</t>
+  </si>
+  <si>
+    <t>VZ</t>
+  </si>
+  <si>
+    <t>AA</t>
   </si>
 </sst>
 </file>
@@ -13886,7 +14504,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
@@ -13933,6 +14551,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13946,6 +14565,23 @@
     <cellStyle name="Normal 5" xfId="4" xr:uid="{6DF54FAE-2483-4EEF-8D6C-A9E4680CE2F0}"/>
   </cellStyles>
   <dxfs count="9">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -14100,23 +14736,6 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -14131,8 +14750,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E01B3177-0B4D-4D90-AD21-322A353B9D10}" name="Table2" displayName="Table2" ref="A1:C19" totalsRowShown="0">
-  <autoFilter ref="A1:C19" xr:uid="{E01B3177-0B4D-4D90-AD21-322A353B9D10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E01B3177-0B4D-4D90-AD21-322A353B9D10}" name="Table2" displayName="Table2" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20" xr:uid="{E01B3177-0B4D-4D90-AD21-322A353B9D10}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3761E3A8-6DA3-4AC8-9E60-9889E5200835}" name="Property Set Name"/>
     <tableColumn id="2" xr3:uid="{33F19375-2CEB-4E6B-994E-E4F9F9266E3A}" name="Property Name"/>
@@ -14143,9 +14762,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:J167" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:J167" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:K211" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:K211" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7CD8FD0B-335F-4B2A-AB69-8C9EE375AC9F}" name="LocationRoot"/>
     <tableColumn id="2" xr3:uid="{E22D17F3-0FB5-4869-9840-DEB0FECC3DC6}" name="SubLocation"/>
     <tableColumn id="3" xr3:uid="{A82C31E6-FA85-4B9B-BA5F-B0D187D6F06D}" name="OrientationID"/>
@@ -14156,28 +14775,29 @@
     <tableColumn id="8" xr3:uid="{3CEB9467-2E3D-4F1E-A4A4-9C65476A8AE5}" name="WorkStep"/>
     <tableColumn id="9" xr3:uid="{B8A60227-91EF-4766-98CB-A9DA957FC5D0}" name="ConstructionPhase"/>
     <tableColumn id="10" xr3:uid="{C2227E0B-2BFC-41C1-97BD-D33A930BE581}" name="AccessConstraint"/>
+    <tableColumn id="11" xr3:uid="{023A7533-A195-4DCA-AC34-BD6926A74239}" name="M&amp;E component ID" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B63" totalsRowShown="0" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B63" totalsRowShown="0" tableBorderDxfId="8">
   <autoFilter ref="A1:B63" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="6" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B166" totalsRowShown="0" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B166" totalsRowShown="0" tableBorderDxfId="5">
   <autoFilter ref="A1:B166" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="3" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14187,8 +14807,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}" name="Table4" displayName="Table4" ref="A1:D3" totalsRowShown="0">
   <autoFilter ref="A1:D3" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A0CDC16A-3706-47C9-9E77-C6678E0326C3}" name="Source Property Name" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{4BC30CBE-C5F5-4A85-8E76-B531F3265739}" name="Target Property Name" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A0CDC16A-3706-47C9-9E77-C6678E0326C3}" name="Source Property Name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{4BC30CBE-C5F5-4A85-8E76-B531F3265739}" name="Target Property Name" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{DF1EFB03-B9BD-43A3-A819-4FC3E2BCCDD0}" name="Function"/>
     <tableColumn id="4" xr3:uid="{F590C646-6614-44AA-8C48-74C4100AC227}" name="Value"/>
   </tableColumns>
@@ -14470,7 +15090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -14591,10 +15211,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>4529</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -14605,7 +15225,7 @@
         <v>4483</v>
       </c>
       <c r="B12" t="s">
-        <v>4484</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -14616,7 +15236,7 @@
         <v>4483</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>4484</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -14627,7 +15247,7 @@
         <v>4483</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -14638,7 +15258,7 @@
         <v>4483</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -14649,10 +15269,10 @@
         <v>4483</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -14660,10 +15280,10 @@
         <v>4483</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -14671,10 +15291,10 @@
         <v>4483</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -14682,9 +15302,20 @@
         <v>4483</v>
       </c>
       <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4483</v>
+      </c>
+      <c r="B20" t="s">
         <v>22</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14698,7 +15329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E22C3A-731E-4720-A4F4-B02EE915C838}">
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:K211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -14711,9 +15342,10 @@
     <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>9</v>
       </c>
@@ -14744,8 +15376,11 @@
       <c r="J1" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="18" t="s">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4505</v>
       </c>
@@ -14776,8 +15411,11 @@
       <c r="J2" t="s">
         <v>4488</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="10" t="s">
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>23</v>
       </c>
@@ -14805,8 +15443,11 @@
       <c r="J3" t="s">
         <v>4490</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="10" t="s">
+        <v>4531</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -14834,8 +15475,11 @@
       <c r="J4" t="s">
         <v>4489</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="10" t="s">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -14860,8 +15504,11 @@
       <c r="H5" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="10" t="s">
+        <v>4533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -14883,8 +15530,11 @@
       <c r="H6" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="10" t="s">
+        <v>4534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -14906,8 +15556,11 @@
       <c r="H7" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="10" t="s">
+        <v>4535</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -14923,8 +15576,11 @@
       <c r="F8" s="10" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="10" t="s">
+        <v>4536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
@@ -14940,8 +15596,11 @@
       <c r="F9" s="10" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="10" t="s">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -14957,8 +15616,11 @@
       <c r="F10" s="10" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="10" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -14974,8 +15636,11 @@
       <c r="F11" s="10" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="10" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -14991,8 +15656,11 @@
       <c r="F12" s="10" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="10" t="s">
+        <v>4540</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -15008,8 +15676,11 @@
       <c r="F13" s="10" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="10" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -15025,8 +15696,11 @@
       <c r="F14" s="10" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="10" t="s">
+        <v>4541</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -15042,8 +15716,11 @@
       <c r="F15" s="10" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -15059,8 +15736,11 @@
       <c r="F16" s="10" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K16" s="10" t="s">
+        <v>4542</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -15073,8 +15753,11 @@
       <c r="E17" s="10" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K17" s="10" t="s">
+        <v>4543</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>38</v>
       </c>
@@ -15087,8 +15770,11 @@
       <c r="E18" s="10" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K18" s="10" t="s">
+        <v>4544</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -15101,8 +15787,11 @@
       <c r="E19" s="10" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K19" s="10" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
@@ -15115,8 +15804,11 @@
       <c r="E20" s="10" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K20" s="10" t="s">
+        <v>4545</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -15126,8 +15818,11 @@
       <c r="D21" s="10" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K21" s="10" t="s">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
@@ -15137,8 +15832,11 @@
       <c r="D22" s="10" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K22" s="10" t="s">
+        <v>4547</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -15148,8 +15846,11 @@
       <c r="D23" s="10" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K23" s="10" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -15159,8 +15860,11 @@
       <c r="D24" s="10" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K24" s="10" t="s">
+        <v>4549</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
@@ -15170,8 +15874,11 @@
       <c r="D25" s="10" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K25" s="10" t="s">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>46</v>
       </c>
@@ -15181,8 +15888,11 @@
       <c r="D26" s="10" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K26" s="10" t="s">
+        <v>4551</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -15192,8 +15902,11 @@
       <c r="D27" s="10" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K27" s="10" t="s">
+        <v>4552</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>48</v>
       </c>
@@ -15203,8 +15916,11 @@
       <c r="D28" s="10" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K28" s="10" t="s">
+        <v>4553</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
@@ -15214,8 +15930,11 @@
       <c r="D29" s="10" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K29" s="10" t="s">
+        <v>4554</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>50</v>
       </c>
@@ -15225,8 +15944,11 @@
       <c r="D30" s="10" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K30" s="10" t="s">
+        <v>4555</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
@@ -15236,8 +15958,11 @@
       <c r="D31" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K31" s="10" t="s">
+        <v>4556</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>52</v>
       </c>
@@ -15247,8 +15972,11 @@
       <c r="D32" s="10" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K32" s="10" t="s">
+        <v>4557</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
@@ -15258,8 +15986,11 @@
       <c r="D33" s="10" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K33" s="10" t="s">
+        <v>4558</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>54</v>
       </c>
@@ -15269,8 +16000,11 @@
       <c r="D34" s="10" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K34" s="10" t="s">
+        <v>4559</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -15280,8 +16014,11 @@
       <c r="D35" s="10" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K35" s="10" t="s">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>56</v>
       </c>
@@ -15291,8 +16028,11 @@
       <c r="D36" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K36" s="10" t="s">
+        <v>4561</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
@@ -15302,8 +16042,11 @@
       <c r="D37" s="10" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K37" s="10" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>58</v>
       </c>
@@ -15313,8 +16056,11 @@
       <c r="D38" s="10" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K38" s="10" t="s">
+        <v>4563</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>59</v>
       </c>
@@ -15324,8 +16070,11 @@
       <c r="D39" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K39" s="10" t="s">
+        <v>4564</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>60</v>
       </c>
@@ -15335,8 +16084,11 @@
       <c r="D40" s="10" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K40" s="10" t="s">
+        <v>4565</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>61</v>
       </c>
@@ -15346,896 +16098,1541 @@
       <c r="D41" s="10" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K41" s="10" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K42" s="10" t="s">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K43" s="10" t="s">
+        <v>4568</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K44" s="10" t="s">
+        <v>4569</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K45" s="10" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K46" s="10" t="s">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K47" s="10" t="s">
+        <v>4572</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K48" s="10" t="s">
+        <v>4573</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>69</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K49" s="10" t="s">
+        <v>4574</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K50" s="10" t="s">
+        <v>4575</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K51" s="10" t="s">
+        <v>4576</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K52" s="10" t="s">
+        <v>4577</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K53" s="10" t="s">
+        <v>4578</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K54" s="10" t="s">
+        <v>4579</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K55" s="10" t="s">
+        <v>4580</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K56" s="10" t="s">
+        <v>4581</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K57" s="10" t="s">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K58" s="10" t="s">
+        <v>4583</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K59" s="10" t="s">
+        <v>4584</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K60" s="10" t="s">
+        <v>4585</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K61" s="10" t="s">
+        <v>4586</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K62" s="10" t="s">
+        <v>4587</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K63" s="10" t="s">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K64" s="10" t="s">
+        <v>4589</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K65" s="10" t="s">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K66" s="10" t="s">
+        <v>4591</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K67" s="10" t="s">
+        <v>4592</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K68" s="10" t="s">
+        <v>4593</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K69" s="10" t="s">
+        <v>4594</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K70" s="10" t="s">
+        <v>4595</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K71" s="10" t="s">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K72" s="10" t="s">
+        <v>4597</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K73" s="10" t="s">
+        <v>4598</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K74" s="10" t="s">
+        <v>4599</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K75" s="10" t="s">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K76" s="10" t="s">
+        <v>4601</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K77" s="10" t="s">
+        <v>4602</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K78" s="10" t="s">
+        <v>4603</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K79" s="10" t="s">
+        <v>4604</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K80" s="10" t="s">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K81" s="10" t="s">
+        <v>4606</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K82" s="10" t="s">
+        <v>4607</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>103</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K83" s="10" t="s">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K84" s="10" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K85" s="10" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K86" s="10" t="s">
+        <v>4611</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>107</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K87" s="10" t="s">
+        <v>4612</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K88" s="10" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K89" s="10" t="s">
+        <v>4614</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K90" s="10" t="s">
+        <v>4615</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>111</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K91" s="10" t="s">
+        <v>4616</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>112</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K92" s="10" t="s">
+        <v>4617</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K93" s="10" t="s">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K94" s="10" t="s">
+        <v>4619</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K95" s="10" t="s">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K96" s="10" t="s">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K97" s="10" t="s">
+        <v>4622</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>118</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K98" s="10" t="s">
+        <v>4623</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K99" s="10" t="s">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K100" s="10" t="s">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>121</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K101" s="10" t="s">
+        <v>4626</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K102" s="10" t="s">
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K103" s="10" t="s">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K104" s="10" t="s">
+        <v>4629</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K105" s="10" t="s">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>4509</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K106" s="10" t="s">
+        <v>4631</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>127</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K107" s="10" t="s">
+        <v>4632</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K108" s="10" t="s">
+        <v>4633</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>128</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K109" s="10" t="s">
+        <v>4634</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>4510</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K110" s="10" t="s">
+        <v>4635</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>4511</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K111" s="10" t="s">
+        <v>4636</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D112" s="10" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K112" s="10" t="s">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>130</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K113" s="10" t="s">
+        <v>4638</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K114" s="10" t="s">
+        <v>4639</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>132</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K115" s="10" t="s">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K116" s="10" t="s">
+        <v>4641</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>134</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K117" s="10" t="s">
+        <v>4642</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>135</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K118" s="10" t="s">
+        <v>4643</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>136</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K119" s="10" t="s">
+        <v>4644</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K120" s="10" t="s">
+        <v>4645</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K121" s="10" t="s">
+        <v>4646</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K122" s="10" t="s">
+        <v>4647</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K123" s="10" t="s">
+        <v>4648</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K124" s="10" t="s">
+        <v>4649</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D125" s="10" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K125" s="10" t="s">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K126" s="10" t="s">
+        <v>4651</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>144</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K127" s="10" t="s">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>145</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K128" s="10" t="s">
+        <v>4653</v>
+      </c>
+    </row>
+    <row r="129" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D129" s="10" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K129" s="10" t="s">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="130" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D130" s="10" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K130" s="10" t="s">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="131" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D131" s="10" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K131" s="10" t="s">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="132" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D132" s="10" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K132" s="10" t="s">
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="133" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D133" s="10" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K133" s="10" t="s">
+        <v>4657</v>
+      </c>
+    </row>
+    <row r="134" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D134" s="10" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K134" s="10" t="s">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="135" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D135" s="10" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K135" s="10" t="s">
+        <v>4659</v>
+      </c>
+    </row>
+    <row r="136" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D136" s="10" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K136" s="10" t="s">
+        <v>4660</v>
+      </c>
+    </row>
+    <row r="137" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D137" s="10" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K137" s="10" t="s">
+        <v>4661</v>
+      </c>
+    </row>
+    <row r="138" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D138" s="10" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K138" s="10" t="s">
+        <v>4662</v>
+      </c>
+    </row>
+    <row r="139" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D139" s="10" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K139" s="10" t="s">
+        <v>4663</v>
+      </c>
+    </row>
+    <row r="140" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D140" s="10" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K140" s="10" t="s">
+        <v>4664</v>
+      </c>
+    </row>
+    <row r="141" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D141" s="10" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K141" s="10" t="s">
+        <v>4665</v>
+      </c>
+    </row>
+    <row r="142" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D142" s="10" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K142" s="10" t="s">
+        <v>4666</v>
+      </c>
+    </row>
+    <row r="143" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D143" s="10" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K143" s="10" t="s">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="144" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D144" s="10" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K144" s="10" t="s">
+        <v>4668</v>
+      </c>
+    </row>
+    <row r="145" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D145" s="10" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K145" s="10" t="s">
+        <v>4669</v>
+      </c>
+    </row>
+    <row r="146" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D146" s="10" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K146" s="10" t="s">
+        <v>4670</v>
+      </c>
+    </row>
+    <row r="147" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D147" s="10" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K147" s="10" t="s">
+        <v>4671</v>
+      </c>
+    </row>
+    <row r="148" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D148" s="10" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K148" s="10" t="s">
+        <v>4672</v>
+      </c>
+    </row>
+    <row r="149" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D149" s="10" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K149" s="10" t="s">
+        <v>4673</v>
+      </c>
+    </row>
+    <row r="150" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D150" s="10" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K150" s="10" t="s">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="151" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D151" s="10" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K151" s="10" t="s">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="152" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D152" s="10" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K152" s="10" t="s">
+        <v>4676</v>
+      </c>
+    </row>
+    <row r="153" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D153" s="10" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K153" s="10" t="s">
+        <v>4677</v>
+      </c>
+    </row>
+    <row r="154" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D154" s="10" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K154" s="10" t="s">
+        <v>4678</v>
+      </c>
+    </row>
+    <row r="155" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D155" s="10" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K155" s="10" t="s">
+        <v>4679</v>
+      </c>
+    </row>
+    <row r="156" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D156" s="10" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K156" s="10" t="s">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="157" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D157" s="10" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K157" s="10" t="s">
+        <v>4681</v>
+      </c>
+    </row>
+    <row r="158" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D158" s="10" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K158" s="10" t="s">
+        <v>4682</v>
+      </c>
+    </row>
+    <row r="159" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D159" s="10" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K159" s="10" t="s">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="160" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D160" s="10" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K160" s="10" t="s">
+        <v>4684</v>
+      </c>
+    </row>
+    <row r="161" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D161" s="10" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K161" s="10" t="s">
+        <v>4685</v>
+      </c>
+    </row>
+    <row r="162" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D162" s="10" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K162" s="10" t="s">
+        <v>4686</v>
+      </c>
+    </row>
+    <row r="163" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D163" s="10" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K163" s="10" t="s">
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="164" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D164" s="10" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K164" s="10" t="s">
+        <v>4688</v>
+      </c>
+    </row>
+    <row r="165" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D165" s="10" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K165" s="10" t="s">
+        <v>4689</v>
+      </c>
+    </row>
+    <row r="166" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D166" s="10" t="s">
         <v>4506</v>
       </c>
-    </row>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="K166" s="10" t="s">
+        <v>4690</v>
+      </c>
+    </row>
+    <row r="167" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D167" s="10" t="s">
         <v>4528</v>
+      </c>
+      <c r="K167" s="10" t="s">
+        <v>4691</v>
+      </c>
+    </row>
+    <row r="168" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D168" s="26"/>
+      <c r="K168" s="10" t="s">
+        <v>4692</v>
+      </c>
+    </row>
+    <row r="169" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D169" s="26"/>
+      <c r="K169" s="10" t="s">
+        <v>4693</v>
+      </c>
+    </row>
+    <row r="170" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D170" s="26"/>
+      <c r="K170" s="10" t="s">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="171" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D171" s="26"/>
+      <c r="K171" s="10" t="s">
+        <v>4695</v>
+      </c>
+    </row>
+    <row r="172" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D172" s="26"/>
+      <c r="K172" s="10" t="s">
+        <v>4696</v>
+      </c>
+    </row>
+    <row r="173" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D173" s="26"/>
+      <c r="K173" s="10" t="s">
+        <v>4697</v>
+      </c>
+    </row>
+    <row r="174" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D174" s="26"/>
+      <c r="K174" s="10" t="s">
+        <v>4698</v>
+      </c>
+    </row>
+    <row r="175" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D175" s="26"/>
+      <c r="K175" s="10" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="176" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D176" s="26"/>
+      <c r="K176" s="10" t="s">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="177" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D177" s="26"/>
+      <c r="K177" s="10" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="178" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D178" s="26"/>
+      <c r="K178" s="10" t="s">
+        <v>4702</v>
+      </c>
+    </row>
+    <row r="179" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D179" s="26"/>
+      <c r="K179" s="10" t="s">
+        <v>4703</v>
+      </c>
+    </row>
+    <row r="180" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D180" s="26"/>
+      <c r="K180" s="10" t="s">
+        <v>4704</v>
+      </c>
+    </row>
+    <row r="181" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D181" s="26"/>
+      <c r="K181" s="10" t="s">
+        <v>4705</v>
+      </c>
+    </row>
+    <row r="182" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D182" s="26"/>
+      <c r="K182" s="10" t="s">
+        <v>4706</v>
+      </c>
+    </row>
+    <row r="183" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D183" s="26"/>
+      <c r="K183" s="10" t="s">
+        <v>4707</v>
+      </c>
+    </row>
+    <row r="184" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D184" s="26"/>
+      <c r="K184" s="10" t="s">
+        <v>4708</v>
+      </c>
+    </row>
+    <row r="185" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D185" s="26"/>
+      <c r="K185" s="10" t="s">
+        <v>4709</v>
+      </c>
+    </row>
+    <row r="186" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D186" s="26"/>
+      <c r="K186" s="10" t="s">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="187" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D187" s="26"/>
+      <c r="K187" s="10" t="s">
+        <v>4711</v>
+      </c>
+    </row>
+    <row r="188" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D188" s="26"/>
+      <c r="K188" s="10" t="s">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="189" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D189" s="26"/>
+      <c r="K189" s="10" t="s">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="190" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D190" s="26"/>
+      <c r="K190" s="10" t="s">
+        <v>4714</v>
+      </c>
+    </row>
+    <row r="191" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D191" s="26"/>
+      <c r="K191" s="10" t="s">
+        <v>4715</v>
+      </c>
+    </row>
+    <row r="192" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D192" s="26"/>
+      <c r="K192" s="10" t="s">
+        <v>4716</v>
+      </c>
+    </row>
+    <row r="193" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D193" s="26"/>
+      <c r="K193" s="10" t="s">
+        <v>4717</v>
+      </c>
+    </row>
+    <row r="194" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D194" s="26"/>
+      <c r="K194" s="10" t="s">
+        <v>4718</v>
+      </c>
+    </row>
+    <row r="195" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D195" s="26"/>
+      <c r="K195" s="10" t="s">
+        <v>4719</v>
+      </c>
+    </row>
+    <row r="196" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D196" s="26"/>
+      <c r="K196" s="10" t="s">
+        <v>4720</v>
+      </c>
+    </row>
+    <row r="197" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D197" s="26"/>
+      <c r="K197" s="10" t="s">
+        <v>4721</v>
+      </c>
+    </row>
+    <row r="198" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D198" s="26"/>
+      <c r="K198" s="10" t="s">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="199" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D199" s="26"/>
+      <c r="K199" s="10" t="s">
+        <v>4723</v>
+      </c>
+    </row>
+    <row r="200" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D200" s="26"/>
+      <c r="K200" s="10" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="201" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D201" s="26"/>
+      <c r="K201" s="10" t="s">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="202" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D202" s="26"/>
+      <c r="K202" s="10" t="s">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="203" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D203" s="26"/>
+      <c r="K203" s="10" t="s">
+        <v>4727</v>
+      </c>
+    </row>
+    <row r="204" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D204" s="26"/>
+      <c r="K204" s="10" t="s">
+        <v>4728</v>
+      </c>
+    </row>
+    <row r="205" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D205" s="26"/>
+      <c r="K205" s="10" t="s">
+        <v>4729</v>
+      </c>
+    </row>
+    <row r="206" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D206" s="26"/>
+      <c r="K206" s="10" t="s">
+        <v>4730</v>
+      </c>
+    </row>
+    <row r="207" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D207" s="26"/>
+      <c r="K207" s="10" t="s">
+        <v>4731</v>
+      </c>
+    </row>
+    <row r="208" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D208" s="26"/>
+      <c r="K208" s="10" t="s">
+        <v>4732</v>
+      </c>
+    </row>
+    <row r="209" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D209" s="26"/>
+      <c r="K209" s="10" t="s">
+        <v>4733</v>
+      </c>
+    </row>
+    <row r="210" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D210" s="26"/>
+      <c r="K210" s="10" t="s">
+        <v>4734</v>
+      </c>
+    </row>
+    <row r="211" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D211" s="26"/>
+      <c r="K211" s="26" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
+++ b/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supi\source\repos\IfcManager\IfcManager.BL\Files\IfcManagerFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800E70F0-B0A2-455C-94B6-CFD62C3DC323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD12315C-BDEA-48F7-B7E0-357E6DF4A66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="745" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="3000" windowWidth="38700" windowHeight="15345" tabRatio="745" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7466" uniqueCount="4735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7468" uniqueCount="4736">
   <si>
     <t>Data Type</t>
   </si>
@@ -13499,9 +13499,6 @@
     <t>4DGroup</t>
   </si>
   <si>
-    <t>&lt;ConstructionPhase&gt;.&lt;WBSID&gt;.&lt;TypeID&gt;.&lt;WorkStep&gt;</t>
-  </si>
-  <si>
     <t>Composed Property Name</t>
   </si>
   <si>
@@ -14247,6 +14244,12 @@
   </si>
   <si>
     <t>AA</t>
+  </si>
+  <si>
+    <t>&lt;LocationRoot&gt;.&lt;SubLocation&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ConstructionPhase&gt;.&lt;WBSID&gt;.&lt;4DGroup&gt;.&lt;WorkStep&gt;</t>
   </si>
 </sst>
 </file>
@@ -14504,7 +14507,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
@@ -14551,7 +14554,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14565,23 +14567,6 @@
     <cellStyle name="Normal 5" xfId="4" xr:uid="{6DF54FAE-2483-4EEF-8D6C-A9E4680CE2F0}"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -14736,6 +14721,23 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -14762,7 +14764,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:K211" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:K211" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A1:K211" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7CD8FD0B-335F-4B2A-AB69-8C9EE375AC9F}" name="LocationRoot"/>
@@ -14782,22 +14784,22 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B63" totalsRowShown="0" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B63" totalsRowShown="0" tableBorderDxfId="7">
   <autoFilter ref="A1:B63" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="7" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="5" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B166" totalsRowShown="0" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B166" totalsRowShown="0" tableBorderDxfId="4">
   <autoFilter ref="A1:B166" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="4" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="2" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14807,8 +14809,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}" name="Table4" displayName="Table4" ref="A1:D3" totalsRowShown="0">
   <autoFilter ref="A1:D3" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A0CDC16A-3706-47C9-9E77-C6678E0326C3}" name="Source Property Name" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{4BC30CBE-C5F5-4A85-8E76-B531F3265739}" name="Target Property Name" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{A0CDC16A-3706-47C9-9E77-C6678E0326C3}" name="Source Property Name" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4BC30CBE-C5F5-4A85-8E76-B531F3265739}" name="Target Property Name" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{DF1EFB03-B9BD-43A3-A819-4FC3E2BCCDD0}" name="Function"/>
     <tableColumn id="4" xr3:uid="{F590C646-6614-44AA-8C48-74C4100AC227}" name="Value"/>
   </tableColumns>
@@ -14817,8 +14819,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{787765E3-921D-4E63-9258-59BCAD55F418}" name="Table5" displayName="Table5" ref="A1:B2" totalsRowShown="0">
-  <autoFilter ref="A1:B2" xr:uid="{787765E3-921D-4E63-9258-59BCAD55F418}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{787765E3-921D-4E63-9258-59BCAD55F418}" name="Table5" displayName="Table5" ref="A1:B3" totalsRowShown="0">
+  <autoFilter ref="A1:B3" xr:uid="{787765E3-921D-4E63-9258-59BCAD55F418}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{9376B07F-8A62-463F-AE6A-A76CBCC974E7}" name="Composed Property Name"/>
     <tableColumn id="2" xr3:uid="{FA9A6ED2-250E-4871-BE11-0909A77AA28F}" name="Formula"/>
@@ -15214,7 +15216,7 @@
         <v>4482</v>
       </c>
       <c r="B11" t="s">
-        <v>4529</v>
+        <v>4528</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -15377,12 +15379,12 @@
         <v>22</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>4529</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4505</v>
+        <v>4504</v>
       </c>
       <c r="B2" t="s">
         <v>159</v>
@@ -15406,13 +15408,13 @@
         <v>358</v>
       </c>
       <c r="I2" t="s">
-        <v>4508</v>
+        <v>4507</v>
       </c>
       <c r="J2" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>4530</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -15441,10 +15443,10 @@
         <v>359</v>
       </c>
       <c r="J3" t="s">
-        <v>4490</v>
+        <v>4489</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>4531</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -15473,10 +15475,10 @@
         <v>360</v>
       </c>
       <c r="J4" t="s">
-        <v>4489</v>
+        <v>4488</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>4532</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -15505,7 +15507,7 @@
         <v>361</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>4533</v>
+        <v>4532</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -15531,7 +15533,7 @@
         <v>362</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>4534</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -15557,7 +15559,7 @@
         <v>363</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>4535</v>
+        <v>4534</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -15577,7 +15579,7 @@
         <v>356</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -15597,7 +15599,7 @@
         <v>357</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>4537</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -15617,7 +15619,7 @@
         <v>243</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>4538</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -15637,7 +15639,7 @@
         <v>251</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>4539</v>
+        <v>4538</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -15657,7 +15659,7 @@
         <v>262</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>4540</v>
+        <v>4539</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -15697,7 +15699,7 @@
         <v>278</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>4541</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -15737,7 +15739,7 @@
         <v>309</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>4542</v>
+        <v>4541</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -15754,7 +15756,7 @@
         <v>343</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>4543</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -15771,7 +15773,7 @@
         <v>344</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>4544</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -15805,7 +15807,7 @@
         <v>346</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>4545</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -15819,7 +15821,7 @@
         <v>179</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>4546</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -15833,7 +15835,7 @@
         <v>180</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>4547</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -15847,7 +15849,7 @@
         <v>181</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>4548</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -15861,7 +15863,7 @@
         <v>182</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>4549</v>
+        <v>4548</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -15875,7 +15877,7 @@
         <v>183</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>4550</v>
+        <v>4549</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -15883,13 +15885,13 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>4512</v>
+        <v>4511</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>184</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>4551</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -15897,13 +15899,13 @@
         <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>4513</v>
+        <v>4512</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>185</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>4552</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -15911,13 +15913,13 @@
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>4514</v>
+        <v>4513</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>186</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>4553</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -15925,13 +15927,13 @@
         <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>4515</v>
+        <v>4514</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>187</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>4554</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -15939,13 +15941,13 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>4516</v>
+        <v>4515</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>188</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>4555</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -15953,13 +15955,13 @@
         <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>4517</v>
+        <v>4516</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>189</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>4556</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -15967,13 +15969,13 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>4518</v>
+        <v>4517</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>190</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>4557</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -15981,13 +15983,13 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>4519</v>
+        <v>4518</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>191</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>4558</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -15995,13 +15997,13 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>4520</v>
+        <v>4519</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>192</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>4559</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -16009,13 +16011,13 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>4521</v>
+        <v>4520</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>193</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>4560</v>
+        <v>4559</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -16023,13 +16025,13 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>4522</v>
+        <v>4521</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>194</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>4561</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -16037,13 +16039,13 @@
         <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>4523</v>
+        <v>4522</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>195</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -16051,13 +16053,13 @@
         <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>4524</v>
+        <v>4523</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>196</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>4563</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -16065,13 +16067,13 @@
         <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>4525</v>
+        <v>4524</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>197</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>4564</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -16079,13 +16081,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>4526</v>
+        <v>4525</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>198</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>4565</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -16093,13 +16095,13 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>4527</v>
+        <v>4526</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>199</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>4566</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -16110,7 +16112,7 @@
         <v>200</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>4567</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -16121,7 +16123,7 @@
         <v>201</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>4568</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -16132,7 +16134,7 @@
         <v>202</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>4569</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -16143,7 +16145,7 @@
         <v>203</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>4570</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -16154,7 +16156,7 @@
         <v>204</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>4571</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -16165,7 +16167,7 @@
         <v>205</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>4572</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -16176,7 +16178,7 @@
         <v>206</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -16187,7 +16189,7 @@
         <v>207</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>4574</v>
+        <v>4573</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -16198,7 +16200,7 @@
         <v>208</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>4575</v>
+        <v>4574</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -16209,7 +16211,7 @@
         <v>209</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>4576</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -16220,7 +16222,7 @@
         <v>210</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>4577</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -16231,7 +16233,7 @@
         <v>211</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>4578</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -16242,7 +16244,7 @@
         <v>212</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>4579</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -16253,7 +16255,7 @@
         <v>213</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>4580</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -16264,7 +16266,7 @@
         <v>214</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>4581</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -16275,7 +16277,7 @@
         <v>215</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>4582</v>
+        <v>4581</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -16286,7 +16288,7 @@
         <v>216</v>
       </c>
       <c r="K58" s="10" t="s">
-        <v>4583</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -16297,7 +16299,7 @@
         <v>217</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>4584</v>
+        <v>4583</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -16308,7 +16310,7 @@
         <v>219</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>4585</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -16319,7 +16321,7 @@
         <v>220</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>4586</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -16330,7 +16332,7 @@
         <v>221</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>4587</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -16341,7 +16343,7 @@
         <v>222</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>4588</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -16352,7 +16354,7 @@
         <v>219</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>4589</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -16363,7 +16365,7 @@
         <v>220</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>4590</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -16374,7 +16376,7 @@
         <v>221</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>4591</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -16385,7 +16387,7 @@
         <v>222</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>4592</v>
+        <v>4591</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -16396,7 +16398,7 @@
         <v>223</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>4593</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -16407,7 +16409,7 @@
         <v>224</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>4594</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -16418,7 +16420,7 @@
         <v>225</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>4595</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -16429,7 +16431,7 @@
         <v>226</v>
       </c>
       <c r="K71" s="10" t="s">
-        <v>4596</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -16440,7 +16442,7 @@
         <v>227</v>
       </c>
       <c r="K72" s="10" t="s">
-        <v>4597</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -16451,7 +16453,7 @@
         <v>228</v>
       </c>
       <c r="K73" s="10" t="s">
-        <v>4598</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -16462,7 +16464,7 @@
         <v>229</v>
       </c>
       <c r="K74" s="10" t="s">
-        <v>4599</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -16473,7 +16475,7 @@
         <v>230</v>
       </c>
       <c r="K75" s="10" t="s">
-        <v>4600</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -16484,7 +16486,7 @@
         <v>231</v>
       </c>
       <c r="K76" s="10" t="s">
-        <v>4601</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -16495,7 +16497,7 @@
         <v>232</v>
       </c>
       <c r="K77" s="10" t="s">
-        <v>4602</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -16506,7 +16508,7 @@
         <v>233</v>
       </c>
       <c r="K78" s="10" t="s">
-        <v>4603</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -16517,7 +16519,7 @@
         <v>234</v>
       </c>
       <c r="K79" s="10" t="s">
-        <v>4604</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -16528,7 +16530,7 @@
         <v>235</v>
       </c>
       <c r="K80" s="10" t="s">
-        <v>4605</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -16539,7 +16541,7 @@
         <v>236</v>
       </c>
       <c r="K81" s="10" t="s">
-        <v>4606</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -16550,7 +16552,7 @@
         <v>237</v>
       </c>
       <c r="K82" s="10" t="s">
-        <v>4607</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -16561,7 +16563,7 @@
         <v>238</v>
       </c>
       <c r="K83" s="10" t="s">
-        <v>4608</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -16572,7 +16574,7 @@
         <v>239</v>
       </c>
       <c r="K84" s="10" t="s">
-        <v>4609</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -16583,7 +16585,7 @@
         <v>240</v>
       </c>
       <c r="K85" s="10" t="s">
-        <v>4610</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -16594,7 +16596,7 @@
         <v>241</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>4611</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -16605,7 +16607,7 @@
         <v>242</v>
       </c>
       <c r="K87" s="10" t="s">
-        <v>4612</v>
+        <v>4611</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -16616,7 +16618,7 @@
         <v>244</v>
       </c>
       <c r="K88" s="10" t="s">
-        <v>4613</v>
+        <v>4612</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -16627,7 +16629,7 @@
         <v>245</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>4614</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -16638,7 +16640,7 @@
         <v>246</v>
       </c>
       <c r="K90" s="10" t="s">
-        <v>4615</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -16649,7 +16651,7 @@
         <v>247</v>
       </c>
       <c r="K91" s="10" t="s">
-        <v>4616</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -16660,7 +16662,7 @@
         <v>248</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>4617</v>
+        <v>4616</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -16671,7 +16673,7 @@
         <v>249</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>4618</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -16682,7 +16684,7 @@
         <v>250</v>
       </c>
       <c r="K94" s="10" t="s">
-        <v>4619</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -16693,7 +16695,7 @@
         <v>252</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>4620</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -16704,7 +16706,7 @@
         <v>253</v>
       </c>
       <c r="K96" s="10" t="s">
-        <v>4621</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -16715,7 +16717,7 @@
         <v>254</v>
       </c>
       <c r="K97" s="10" t="s">
-        <v>4622</v>
+        <v>4621</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -16726,7 +16728,7 @@
         <v>255</v>
       </c>
       <c r="K98" s="10" t="s">
-        <v>4623</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -16737,7 +16739,7 @@
         <v>256</v>
       </c>
       <c r="K99" s="10" t="s">
-        <v>4624</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -16748,7 +16750,7 @@
         <v>257</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>4625</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -16759,7 +16761,7 @@
         <v>258</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>4626</v>
+        <v>4625</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -16770,7 +16772,7 @@
         <v>259</v>
       </c>
       <c r="K102" s="10" t="s">
-        <v>4627</v>
+        <v>4626</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -16781,7 +16783,7 @@
         <v>260</v>
       </c>
       <c r="K103" s="10" t="s">
-        <v>4628</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -16792,7 +16794,7 @@
         <v>261</v>
       </c>
       <c r="K104" s="10" t="s">
-        <v>4629</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -16803,18 +16805,18 @@
         <v>263</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>4630</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>264</v>
       </c>
       <c r="K106" s="10" t="s">
-        <v>4631</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -16825,7 +16827,7 @@
         <v>265</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>4632</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -16836,7 +16838,7 @@
         <v>266</v>
       </c>
       <c r="K108" s="10" t="s">
-        <v>4633</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -16847,29 +16849,29 @@
         <v>267</v>
       </c>
       <c r="K109" s="10" t="s">
-        <v>4634</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>4510</v>
+        <v>4509</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>268</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>4635</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>4511</v>
+        <v>4510</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>269</v>
       </c>
       <c r="K111" s="10" t="s">
-        <v>4636</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -16880,7 +16882,7 @@
         <v>271</v>
       </c>
       <c r="K112" s="10" t="s">
-        <v>4637</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -16891,7 +16893,7 @@
         <v>272</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>4638</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -16902,7 +16904,7 @@
         <v>273</v>
       </c>
       <c r="K114" s="10" t="s">
-        <v>4639</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -16913,7 +16915,7 @@
         <v>274</v>
       </c>
       <c r="K115" s="10" t="s">
-        <v>4640</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -16924,7 +16926,7 @@
         <v>275</v>
       </c>
       <c r="K116" s="10" t="s">
-        <v>4641</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -16935,7 +16937,7 @@
         <v>276</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>4642</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -16946,7 +16948,7 @@
         <v>277</v>
       </c>
       <c r="K118" s="10" t="s">
-        <v>4643</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -16957,7 +16959,7 @@
         <v>279</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>4644</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -16968,7 +16970,7 @@
         <v>280</v>
       </c>
       <c r="K120" s="10" t="s">
-        <v>4645</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -16979,7 +16981,7 @@
         <v>281</v>
       </c>
       <c r="K121" s="10" t="s">
-        <v>4646</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -16990,7 +16992,7 @@
         <v>282</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>4647</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -17001,7 +17003,7 @@
         <v>283</v>
       </c>
       <c r="K123" s="10" t="s">
-        <v>4648</v>
+        <v>4647</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -17012,7 +17014,7 @@
         <v>285</v>
       </c>
       <c r="K124" s="10" t="s">
-        <v>4649</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -17023,7 +17025,7 @@
         <v>286</v>
       </c>
       <c r="K125" s="10" t="s">
-        <v>4650</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -17034,7 +17036,7 @@
         <v>287</v>
       </c>
       <c r="K126" s="10" t="s">
-        <v>4651</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -17045,7 +17047,7 @@
         <v>288</v>
       </c>
       <c r="K127" s="10" t="s">
-        <v>4652</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -17056,7 +17058,7 @@
         <v>289</v>
       </c>
       <c r="K128" s="10" t="s">
-        <v>4653</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="129" spans="4:11" x14ac:dyDescent="0.25">
@@ -17064,7 +17066,7 @@
         <v>290</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>4637</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="130" spans="4:11" x14ac:dyDescent="0.25">
@@ -17072,7 +17074,7 @@
         <v>291</v>
       </c>
       <c r="K130" s="10" t="s">
-        <v>4654</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="131" spans="4:11" x14ac:dyDescent="0.25">
@@ -17080,7 +17082,7 @@
         <v>292</v>
       </c>
       <c r="K131" s="10" t="s">
-        <v>4655</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="132" spans="4:11" x14ac:dyDescent="0.25">
@@ -17088,7 +17090,7 @@
         <v>293</v>
       </c>
       <c r="K132" s="10" t="s">
-        <v>4656</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="133" spans="4:11" x14ac:dyDescent="0.25">
@@ -17096,7 +17098,7 @@
         <v>294</v>
       </c>
       <c r="K133" s="10" t="s">
-        <v>4657</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="134" spans="4:11" x14ac:dyDescent="0.25">
@@ -17104,7 +17106,7 @@
         <v>295</v>
       </c>
       <c r="K134" s="10" t="s">
-        <v>4658</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="135" spans="4:11" x14ac:dyDescent="0.25">
@@ -17112,7 +17114,7 @@
         <v>296</v>
       </c>
       <c r="K135" s="10" t="s">
-        <v>4659</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="136" spans="4:11" x14ac:dyDescent="0.25">
@@ -17120,7 +17122,7 @@
         <v>297</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>4660</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="137" spans="4:11" x14ac:dyDescent="0.25">
@@ -17128,7 +17130,7 @@
         <v>298</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>4661</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="138" spans="4:11" x14ac:dyDescent="0.25">
@@ -17136,7 +17138,7 @@
         <v>299</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>4662</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="139" spans="4:11" x14ac:dyDescent="0.25">
@@ -17144,7 +17146,7 @@
         <v>300</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>4663</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="140" spans="4:11" x14ac:dyDescent="0.25">
@@ -17152,7 +17154,7 @@
         <v>301</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>4664</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="141" spans="4:11" x14ac:dyDescent="0.25">
@@ -17160,7 +17162,7 @@
         <v>302</v>
       </c>
       <c r="K141" s="10" t="s">
-        <v>4665</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="142" spans="4:11" x14ac:dyDescent="0.25">
@@ -17168,7 +17170,7 @@
         <v>303</v>
       </c>
       <c r="K142" s="10" t="s">
-        <v>4666</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="143" spans="4:11" x14ac:dyDescent="0.25">
@@ -17176,7 +17178,7 @@
         <v>304</v>
       </c>
       <c r="K143" s="10" t="s">
-        <v>4667</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="144" spans="4:11" x14ac:dyDescent="0.25">
@@ -17184,7 +17186,7 @@
         <v>305</v>
       </c>
       <c r="K144" s="10" t="s">
-        <v>4668</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="145" spans="4:11" x14ac:dyDescent="0.25">
@@ -17192,7 +17194,7 @@
         <v>306</v>
       </c>
       <c r="K145" s="10" t="s">
-        <v>4669</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="146" spans="4:11" x14ac:dyDescent="0.25">
@@ -17200,7 +17202,7 @@
         <v>307</v>
       </c>
       <c r="K146" s="10" t="s">
-        <v>4670</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="147" spans="4:11" x14ac:dyDescent="0.25">
@@ -17208,7 +17210,7 @@
         <v>308</v>
       </c>
       <c r="K147" s="10" t="s">
-        <v>4671</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="148" spans="4:11" x14ac:dyDescent="0.25">
@@ -17216,7 +17218,7 @@
         <v>310</v>
       </c>
       <c r="K148" s="10" t="s">
-        <v>4672</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="149" spans="4:11" x14ac:dyDescent="0.25">
@@ -17224,7 +17226,7 @@
         <v>311</v>
       </c>
       <c r="K149" s="10" t="s">
-        <v>4673</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="150" spans="4:11" x14ac:dyDescent="0.25">
@@ -17232,7 +17234,7 @@
         <v>312</v>
       </c>
       <c r="K150" s="10" t="s">
-        <v>4674</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="151" spans="4:11" x14ac:dyDescent="0.25">
@@ -17240,7 +17242,7 @@
         <v>313</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>4675</v>
+        <v>4674</v>
       </c>
     </row>
     <row r="152" spans="4:11" x14ac:dyDescent="0.25">
@@ -17248,7 +17250,7 @@
         <v>314</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>4676</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="153" spans="4:11" x14ac:dyDescent="0.25">
@@ -17256,7 +17258,7 @@
         <v>315</v>
       </c>
       <c r="K153" s="10" t="s">
-        <v>4677</v>
+        <v>4676</v>
       </c>
     </row>
     <row r="154" spans="4:11" x14ac:dyDescent="0.25">
@@ -17264,7 +17266,7 @@
         <v>316</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>4678</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="155" spans="4:11" x14ac:dyDescent="0.25">
@@ -17272,7 +17274,7 @@
         <v>317</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>4679</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="156" spans="4:11" x14ac:dyDescent="0.25">
@@ -17280,7 +17282,7 @@
         <v>318</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>4680</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="157" spans="4:11" x14ac:dyDescent="0.25">
@@ -17288,7 +17290,7 @@
         <v>319</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>4681</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="158" spans="4:11" x14ac:dyDescent="0.25">
@@ -17296,7 +17298,7 @@
         <v>320</v>
       </c>
       <c r="K158" s="10" t="s">
-        <v>4682</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="159" spans="4:11" x14ac:dyDescent="0.25">
@@ -17304,7 +17306,7 @@
         <v>321</v>
       </c>
       <c r="K159" s="10" t="s">
-        <v>4683</v>
+        <v>4682</v>
       </c>
     </row>
     <row r="160" spans="4:11" x14ac:dyDescent="0.25">
@@ -17312,7 +17314,7 @@
         <v>322</v>
       </c>
       <c r="K160" s="10" t="s">
-        <v>4684</v>
+        <v>4683</v>
       </c>
     </row>
     <row r="161" spans="4:11" x14ac:dyDescent="0.25">
@@ -17320,7 +17322,7 @@
         <v>323</v>
       </c>
       <c r="K161" s="10" t="s">
-        <v>4685</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="162" spans="4:11" x14ac:dyDescent="0.25">
@@ -17328,7 +17330,7 @@
         <v>324</v>
       </c>
       <c r="K162" s="10" t="s">
-        <v>4686</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="163" spans="4:11" x14ac:dyDescent="0.25">
@@ -17336,7 +17338,7 @@
         <v>325</v>
       </c>
       <c r="K163" s="10" t="s">
-        <v>4687</v>
+        <v>4686</v>
       </c>
     </row>
     <row r="164" spans="4:11" x14ac:dyDescent="0.25">
@@ -17344,7 +17346,7 @@
         <v>326</v>
       </c>
       <c r="K164" s="10" t="s">
-        <v>4688</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="165" spans="4:11" x14ac:dyDescent="0.25">
@@ -17352,286 +17354,286 @@
         <v>327</v>
       </c>
       <c r="K165" s="10" t="s">
-        <v>4689</v>
+        <v>4688</v>
       </c>
     </row>
     <row r="166" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D166" s="10" t="s">
-        <v>4506</v>
+        <v>4505</v>
       </c>
       <c r="K166" s="10" t="s">
-        <v>4690</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="167" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D167" s="10" t="s">
-        <v>4528</v>
+        <v>4527</v>
       </c>
       <c r="K167" s="10" t="s">
+        <v>4690</v>
+      </c>
+    </row>
+    <row r="168" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D168" s="10"/>
+      <c r="K168" s="10" t="s">
         <v>4691</v>
       </c>
     </row>
-    <row r="168" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D168" s="26"/>
-      <c r="K168" s="10" t="s">
+    <row r="169" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D169" s="10"/>
+      <c r="K169" s="10" t="s">
         <v>4692</v>
       </c>
     </row>
-    <row r="169" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D169" s="26"/>
-      <c r="K169" s="10" t="s">
+    <row r="170" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D170" s="10"/>
+      <c r="K170" s="10" t="s">
         <v>4693</v>
       </c>
     </row>
-    <row r="170" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D170" s="26"/>
-      <c r="K170" s="10" t="s">
+    <row r="171" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D171" s="10"/>
+      <c r="K171" s="10" t="s">
         <v>4694</v>
       </c>
     </row>
-    <row r="171" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D171" s="26"/>
-      <c r="K171" s="10" t="s">
+    <row r="172" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D172" s="10"/>
+      <c r="K172" s="10" t="s">
         <v>4695</v>
       </c>
     </row>
-    <row r="172" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D172" s="26"/>
-      <c r="K172" s="10" t="s">
+    <row r="173" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D173" s="10"/>
+      <c r="K173" s="10" t="s">
         <v>4696</v>
       </c>
     </row>
-    <row r="173" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D173" s="26"/>
-      <c r="K173" s="10" t="s">
+    <row r="174" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D174" s="10"/>
+      <c r="K174" s="10" t="s">
         <v>4697</v>
       </c>
     </row>
-    <row r="174" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D174" s="26"/>
-      <c r="K174" s="10" t="s">
+    <row r="175" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D175" s="10"/>
+      <c r="K175" s="10" t="s">
         <v>4698</v>
       </c>
     </row>
-    <row r="175" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D175" s="26"/>
-      <c r="K175" s="10" t="s">
+    <row r="176" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D176" s="10"/>
+      <c r="K176" s="10" t="s">
         <v>4699</v>
       </c>
     </row>
-    <row r="176" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D176" s="26"/>
-      <c r="K176" s="10" t="s">
+    <row r="177" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D177" s="10"/>
+      <c r="K177" s="10" t="s">
         <v>4700</v>
       </c>
     </row>
-    <row r="177" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D177" s="26"/>
-      <c r="K177" s="10" t="s">
+    <row r="178" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D178" s="10"/>
+      <c r="K178" s="10" t="s">
         <v>4701</v>
       </c>
     </row>
-    <row r="178" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D178" s="26"/>
-      <c r="K178" s="10" t="s">
+    <row r="179" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D179" s="10"/>
+      <c r="K179" s="10" t="s">
         <v>4702</v>
       </c>
     </row>
-    <row r="179" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D179" s="26"/>
-      <c r="K179" s="10" t="s">
+    <row r="180" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D180" s="10"/>
+      <c r="K180" s="10" t="s">
         <v>4703</v>
       </c>
     </row>
-    <row r="180" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D180" s="26"/>
-      <c r="K180" s="10" t="s">
+    <row r="181" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D181" s="10"/>
+      <c r="K181" s="10" t="s">
         <v>4704</v>
       </c>
     </row>
-    <row r="181" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D181" s="26"/>
-      <c r="K181" s="10" t="s">
+    <row r="182" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D182" s="10"/>
+      <c r="K182" s="10" t="s">
         <v>4705</v>
       </c>
     </row>
-    <row r="182" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D182" s="26"/>
-      <c r="K182" s="10" t="s">
+    <row r="183" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D183" s="10"/>
+      <c r="K183" s="10" t="s">
         <v>4706</v>
       </c>
     </row>
-    <row r="183" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D183" s="26"/>
-      <c r="K183" s="10" t="s">
+    <row r="184" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D184" s="10"/>
+      <c r="K184" s="10" t="s">
         <v>4707</v>
       </c>
     </row>
-    <row r="184" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D184" s="26"/>
-      <c r="K184" s="10" t="s">
+    <row r="185" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D185" s="10"/>
+      <c r="K185" s="10" t="s">
         <v>4708</v>
       </c>
     </row>
-    <row r="185" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D185" s="26"/>
-      <c r="K185" s="10" t="s">
+    <row r="186" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D186" s="10"/>
+      <c r="K186" s="10" t="s">
         <v>4709</v>
       </c>
     </row>
-    <row r="186" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D186" s="26"/>
-      <c r="K186" s="10" t="s">
+    <row r="187" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D187" s="10"/>
+      <c r="K187" s="10" t="s">
         <v>4710</v>
       </c>
     </row>
-    <row r="187" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D187" s="26"/>
-      <c r="K187" s="10" t="s">
+    <row r="188" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D188" s="10"/>
+      <c r="K188" s="10" t="s">
         <v>4711</v>
       </c>
     </row>
-    <row r="188" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D188" s="26"/>
-      <c r="K188" s="10" t="s">
+    <row r="189" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D189" s="10"/>
+      <c r="K189" s="10" t="s">
         <v>4712</v>
       </c>
     </row>
-    <row r="189" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D189" s="26"/>
-      <c r="K189" s="10" t="s">
+    <row r="190" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D190" s="10"/>
+      <c r="K190" s="10" t="s">
         <v>4713</v>
       </c>
     </row>
-    <row r="190" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D190" s="26"/>
-      <c r="K190" s="10" t="s">
+    <row r="191" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D191" s="10"/>
+      <c r="K191" s="10" t="s">
         <v>4714</v>
       </c>
     </row>
-    <row r="191" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D191" s="26"/>
-      <c r="K191" s="10" t="s">
+    <row r="192" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D192" s="10"/>
+      <c r="K192" s="10" t="s">
         <v>4715</v>
       </c>
     </row>
-    <row r="192" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D192" s="26"/>
-      <c r="K192" s="10" t="s">
+    <row r="193" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D193" s="10"/>
+      <c r="K193" s="10" t="s">
         <v>4716</v>
       </c>
     </row>
-    <row r="193" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D193" s="26"/>
-      <c r="K193" s="10" t="s">
+    <row r="194" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D194" s="10"/>
+      <c r="K194" s="10" t="s">
         <v>4717</v>
       </c>
     </row>
-    <row r="194" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D194" s="26"/>
-      <c r="K194" s="10" t="s">
+    <row r="195" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D195" s="10"/>
+      <c r="K195" s="10" t="s">
         <v>4718</v>
       </c>
     </row>
-    <row r="195" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D195" s="26"/>
-      <c r="K195" s="10" t="s">
+    <row r="196" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D196" s="10"/>
+      <c r="K196" s="10" t="s">
         <v>4719</v>
       </c>
     </row>
-    <row r="196" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D196" s="26"/>
-      <c r="K196" s="10" t="s">
+    <row r="197" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D197" s="10"/>
+      <c r="K197" s="10" t="s">
         <v>4720</v>
       </c>
     </row>
-    <row r="197" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D197" s="26"/>
-      <c r="K197" s="10" t="s">
+    <row r="198" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D198" s="10"/>
+      <c r="K198" s="10" t="s">
         <v>4721</v>
       </c>
     </row>
-    <row r="198" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D198" s="26"/>
-      <c r="K198" s="10" t="s">
+    <row r="199" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D199" s="10"/>
+      <c r="K199" s="10" t="s">
         <v>4722</v>
       </c>
     </row>
-    <row r="199" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D199" s="26"/>
-      <c r="K199" s="10" t="s">
+    <row r="200" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D200" s="10"/>
+      <c r="K200" s="10" t="s">
         <v>4723</v>
       </c>
     </row>
-    <row r="200" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D200" s="26"/>
-      <c r="K200" s="10" t="s">
+    <row r="201" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D201" s="10"/>
+      <c r="K201" s="10" t="s">
         <v>4724</v>
       </c>
     </row>
-    <row r="201" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D201" s="26"/>
-      <c r="K201" s="10" t="s">
+    <row r="202" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D202" s="10"/>
+      <c r="K202" s="10" t="s">
         <v>4725</v>
       </c>
     </row>
-    <row r="202" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D202" s="26"/>
-      <c r="K202" s="10" t="s">
+    <row r="203" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D203" s="10"/>
+      <c r="K203" s="10" t="s">
         <v>4726</v>
       </c>
     </row>
-    <row r="203" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D203" s="26"/>
-      <c r="K203" s="10" t="s">
+    <row r="204" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D204" s="10"/>
+      <c r="K204" s="10" t="s">
         <v>4727</v>
       </c>
     </row>
-    <row r="204" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D204" s="26"/>
-      <c r="K204" s="10" t="s">
+    <row r="205" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D205" s="10"/>
+      <c r="K205" s="10" t="s">
         <v>4728</v>
       </c>
     </row>
-    <row r="205" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D205" s="26"/>
-      <c r="K205" s="10" t="s">
+    <row r="206" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D206" s="10"/>
+      <c r="K206" s="10" t="s">
         <v>4729</v>
       </c>
     </row>
-    <row r="206" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D206" s="26"/>
-      <c r="K206" s="10" t="s">
+    <row r="207" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D207" s="10"/>
+      <c r="K207" s="10" t="s">
         <v>4730</v>
       </c>
     </row>
-    <row r="207" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D207" s="26"/>
-      <c r="K207" s="10" t="s">
+    <row r="208" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D208" s="10"/>
+      <c r="K208" s="10" t="s">
         <v>4731</v>
       </c>
     </row>
-    <row r="208" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D208" s="26"/>
-      <c r="K208" s="10" t="s">
+    <row r="209" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D209" s="10"/>
+      <c r="K209" s="10" t="s">
         <v>4732</v>
       </c>
     </row>
-    <row r="209" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D209" s="26"/>
-      <c r="K209" s="10" t="s">
+    <row r="210" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D210" s="10"/>
+      <c r="K210" s="10" t="s">
         <v>4733</v>
       </c>
     </row>
-    <row r="210" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D210" s="26"/>
-      <c r="K210" s="10" t="s">
-        <v>4734</v>
-      </c>
-    </row>
     <row r="211" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D211" s="26"/>
-      <c r="K211" s="26" t="s">
+      <c r="D211" s="10"/>
+      <c r="K211" s="10" t="s">
         <v>159</v>
       </c>
     </row>
@@ -41161,7 +41163,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>4505</v>
+        <v>4504</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>159</v>
@@ -41521,135 +41523,135 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>4512</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>4513</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>4514</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>4515</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>4516</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>4517</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>4518</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>4519</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>4520</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>4521</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>4522</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>4523</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>4524</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>4525</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>4526</v>
+        <v>4525</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>4527</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="B63" s="25" t="s">
         <v>159</v>
@@ -41685,7 +41687,7 @@
         <v>160</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -41693,7 +41695,7 @@
         <v>161</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -41701,7 +41703,7 @@
         <v>162</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -41709,7 +41711,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -41717,7 +41719,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -41725,7 +41727,7 @@
         <v>165</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -41733,7 +41735,7 @@
         <v>166</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -41741,7 +41743,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -41749,7 +41751,7 @@
         <v>168</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -41757,7 +41759,7 @@
         <v>169</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -41765,7 +41767,7 @@
         <v>170</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -41773,7 +41775,7 @@
         <v>171</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -41781,7 +41783,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -41789,7 +41791,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -41797,7 +41799,7 @@
         <v>174</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -41805,7 +41807,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -41813,7 +41815,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -41821,7 +41823,7 @@
         <v>177</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -41829,7 +41831,7 @@
         <v>178</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -41837,7 +41839,7 @@
         <v>179</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -41845,7 +41847,7 @@
         <v>180</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -41853,7 +41855,7 @@
         <v>181</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -41861,7 +41863,7 @@
         <v>182</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -41869,7 +41871,7 @@
         <v>183</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -41877,7 +41879,7 @@
         <v>184</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -41885,7 +41887,7 @@
         <v>185</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -41893,7 +41895,7 @@
         <v>186</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -41901,7 +41903,7 @@
         <v>187</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -41941,7 +41943,7 @@
         <v>192</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>4497</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -41965,7 +41967,7 @@
         <v>195</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>4498</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -41973,7 +41975,7 @@
         <v>196</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>4498</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -41981,7 +41983,7 @@
         <v>197</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -41989,7 +41991,7 @@
         <v>198</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -41997,7 +41999,7 @@
         <v>199</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -42005,7 +42007,7 @@
         <v>200</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -42013,7 +42015,7 @@
         <v>201</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>4500</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -42021,7 +42023,7 @@
         <v>202</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>4501</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -42029,7 +42031,7 @@
         <v>203</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>4501</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -42037,7 +42039,7 @@
         <v>204</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -42045,7 +42047,7 @@
         <v>205</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -42053,7 +42055,7 @@
         <v>206</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -42061,7 +42063,7 @@
         <v>207</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -42069,7 +42071,7 @@
         <v>208</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -42077,7 +42079,7 @@
         <v>209</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -42085,7 +42087,7 @@
         <v>210</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -42093,7 +42095,7 @@
         <v>211</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -42101,7 +42103,7 @@
         <v>212</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -42109,7 +42111,7 @@
         <v>213</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -42117,7 +42119,7 @@
         <v>214</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -42125,7 +42127,7 @@
         <v>215</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -42133,7 +42135,7 @@
         <v>216</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -42141,7 +42143,7 @@
         <v>217</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -42210,10 +42212,10 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>4528</v>
+        <v>4527</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>4528</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -42573,7 +42575,7 @@
         <v>271</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -42581,7 +42583,7 @@
         <v>272</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -42589,7 +42591,7 @@
         <v>273</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -42597,7 +42599,7 @@
         <v>274</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -42605,7 +42607,7 @@
         <v>275</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -42613,7 +42615,7 @@
         <v>276</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -42621,7 +42623,7 @@
         <v>277</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -42629,7 +42631,7 @@
         <v>279</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -42637,7 +42639,7 @@
         <v>280</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -42645,7 +42647,7 @@
         <v>281</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -42653,7 +42655,7 @@
         <v>282</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -42661,7 +42663,7 @@
         <v>283</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -42669,7 +42671,7 @@
         <v>285</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -42677,7 +42679,7 @@
         <v>286</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -42685,7 +42687,7 @@
         <v>287</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -42693,7 +42695,7 @@
         <v>288</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -42701,7 +42703,7 @@
         <v>289</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -42709,7 +42711,7 @@
         <v>290</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -42717,7 +42719,7 @@
         <v>291</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -42725,7 +42727,7 @@
         <v>292</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -42733,7 +42735,7 @@
         <v>293</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -42741,7 +42743,7 @@
         <v>294</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -42749,7 +42751,7 @@
         <v>295</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -42757,7 +42759,7 @@
         <v>296</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -42765,7 +42767,7 @@
         <v>297</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -42773,7 +42775,7 @@
         <v>298</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -42781,7 +42783,7 @@
         <v>299</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -42789,7 +42791,7 @@
         <v>300</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -42797,7 +42799,7 @@
         <v>301</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -42805,7 +42807,7 @@
         <v>302</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -42813,7 +42815,7 @@
         <v>303</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -42821,7 +42823,7 @@
         <v>304</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -42829,7 +42831,7 @@
         <v>306</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -42837,7 +42839,7 @@
         <v>307</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -42845,7 +42847,7 @@
         <v>308</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -42994,10 +42996,10 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="22" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B166" s="10" t="s">
         <v>4506</v>
-      </c>
-      <c r="B166" s="10" t="s">
-        <v>4507</v>
       </c>
     </row>
   </sheetData>
@@ -43030,7 +43032,7 @@
         <v>4480</v>
       </c>
       <c r="D1" t="s">
-        <v>4491</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -43052,7 +43054,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>4492</v>
+        <v>4491</v>
       </c>
       <c r="D3" t="s">
         <v>348</v>
@@ -43068,7 +43070,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F92CC8-C507-429E-80E1-05934A71C4A2}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
@@ -43077,10 +43079,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4485</v>
+      </c>
+      <c r="B1" t="s">
         <v>4486</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4487</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -43088,7 +43090,15 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>4485</v>
+        <v>4735</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4734</v>
       </c>
     </row>
   </sheetData>

--- a/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
+++ b/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supi\source\repos\IfcManager\IfcManager.BL\Files\IfcManagerFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD12315C-BDEA-48F7-B7E0-357E6DF4A66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBE4F34-879F-4479-A536-5A8175BFA926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="3000" windowWidth="38700" windowHeight="15345" tabRatio="745" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22140" yWindow="2910" windowWidth="38700" windowHeight="15345" tabRatio="720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
     <sheet name="Picklist" sheetId="2" r:id="rId2"/>
     <sheet name="Layers Mapping" sheetId="3" r:id="rId3"/>
     <sheet name="LocationRoot Match" sheetId="4" r:id="rId4"/>
-    <sheet name="4DGroup Exact Match" sheetId="7" r:id="rId5"/>
-    <sheet name="Expressions" sheetId="5" r:id="rId6"/>
-    <sheet name="Composed" sheetId="6" r:id="rId7"/>
+    <sheet name="SpaceID Match" sheetId="8" r:id="rId5"/>
+    <sheet name="4DGroup Exact Match" sheetId="7" r:id="rId6"/>
+    <sheet name="Expressions" sheetId="5" r:id="rId7"/>
+    <sheet name="Composed" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7468" uniqueCount="4736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="4774">
   <si>
     <t>Data Type</t>
   </si>
@@ -13556,9 +13557,6 @@
     <t>MEP_INSTALL</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
     <t>STR.NBR</t>
   </si>
   <si>
@@ -14246,17 +14244,134 @@
     <t>AA</t>
   </si>
   <si>
-    <t>&lt;LocationRoot&gt;.&lt;SubLocation&gt;</t>
-  </si>
-  <si>
-    <t>&lt;ConstructionPhase&gt;.&lt;WBSID&gt;.&lt;4DGroup&gt;.&lt;WorkStep&gt;</t>
+    <t>&lt;LocationRoot&gt;.&lt;SubLocation&gt;.&lt;OrientationID&gt;</t>
+  </si>
+  <si>
+    <t>L_0</t>
+  </si>
+  <si>
+    <t>L_-0.5</t>
+  </si>
+  <si>
+    <t>L_-1</t>
+  </si>
+  <si>
+    <t>L_-2</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>TRL</t>
+  </si>
+  <si>
+    <t>RB-13</t>
+  </si>
+  <si>
+    <t>RB-18</t>
+  </si>
+  <si>
+    <t>APR</t>
+  </si>
+  <si>
+    <t>&lt;ConstructionPhase&gt;.&lt;LocationRoot&gt;.&lt;SubLocation&gt;.&lt;OrientationID&gt;.&lt;4DGroup&gt;.&lt;WorkStep&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14344,8 +14459,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -14383,11 +14517,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FF0BBBEF"/>
+        <bgColor rgb="FF0BBBEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCF2FD"/>
+        <bgColor rgb="FFCCF2FD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -14483,15 +14624,22 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color theme="0"/>
       </left>
       <right style="thin">
         <color theme="0"/>
       </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -14507,7 +14655,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
@@ -14549,11 +14697,14 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14566,7 +14717,7 @@
     <cellStyle name="Normal 4 3" xfId="8" xr:uid="{647E405E-89F1-46B3-9D0F-7CADBB992D37}"/>
     <cellStyle name="Normal 5" xfId="4" xr:uid="{6DF54FAE-2483-4EEF-8D6C-A9E4680CE2F0}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="14">
     <dxf>
       <font>
         <b val="0"/>
@@ -14669,6 +14820,37 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.79998168889431442"/>
@@ -14764,9 +14946,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:K211" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A1:K211" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:L211" totalsRowShown="0" headerRowDxfId="13">
+  <autoFilter ref="A1:L211" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{7CD8FD0B-335F-4B2A-AB69-8C9EE375AC9F}" name="LocationRoot"/>
     <tableColumn id="2" xr3:uid="{E22D17F3-0FB5-4869-9840-DEB0FECC3DC6}" name="SubLocation"/>
     <tableColumn id="3" xr3:uid="{A82C31E6-FA85-4B9B-BA5F-B0D187D6F06D}" name="OrientationID"/>
@@ -14778,25 +14960,41 @@
     <tableColumn id="9" xr3:uid="{B8A60227-91EF-4766-98CB-A9DA957FC5D0}" name="ConstructionPhase"/>
     <tableColumn id="10" xr3:uid="{C2227E0B-2BFC-41C1-97BD-D33A930BE581}" name="AccessConstraint"/>
     <tableColumn id="11" xr3:uid="{023A7533-A195-4DCA-AC34-BD6926A74239}" name="M&amp;E component ID" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{1EF8BBD2-7EDC-40AF-B6EA-C9BB48C5E084}" name="SpaceID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B63" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:B63" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B71" totalsRowShown="0" tableBorderDxfId="12">
+  <autoFilter ref="A1:B71" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="11" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="10" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B166" totalsRowShown="0" tableBorderDxfId="4">
-  <autoFilter ref="A1:B166" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{05794BD0-36D1-4902-97E0-542EBA653550}" name="Table8" displayName="Table8" ref="A1:C69" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:C69" xr:uid="{05794BD0-36D1-4902-97E0-542EBA653550}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C69">
+    <sortCondition ref="A1:A69"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{809AE534-87F1-493B-8DE3-D1EF41305073}" name="LocationRoot" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{8AEA72EF-D1C3-4C17-ACDD-D668C0F1C361}" name="SubLocation" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{8522D775-A8DF-46ED-B8DF-932C6B351FDB}" name="SpaceID" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B162" totalsRowShown="0" tableBorderDxfId="4">
+  <autoFilter ref="A1:B162" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="3" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="2" dataCellStyle="Normal 2"/>
@@ -14805,7 +15003,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}" name="Table4" displayName="Table4" ref="A1:D3" totalsRowShown="0">
   <autoFilter ref="A1:D3" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}"/>
   <tableColumns count="4">
@@ -14818,7 +15016,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{787765E3-921D-4E63-9258-59BCAD55F418}" name="Table5" displayName="Table5" ref="A1:B3" totalsRowShown="0">
   <autoFilter ref="A1:B3" xr:uid="{787765E3-921D-4E63-9258-59BCAD55F418}"/>
   <tableColumns count="2">
@@ -15216,7 +15414,7 @@
         <v>4482</v>
       </c>
       <c r="B11" t="s">
-        <v>4528</v>
+        <v>4527</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -15331,7 +15529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E22C3A-731E-4720-A4F4-B02EE915C838}">
-  <dimension ref="A1:K211"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -15345,9 +15543,10 @@
     <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" customWidth="1"/>
     <col min="11" max="11" width="22.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>9</v>
       </c>
@@ -15379,12 +15578,15 @@
         <v>22</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>4528</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4504</v>
+        <v>4527</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="B2" t="s">
         <v>159</v>
@@ -15408,18 +15610,21 @@
         <v>358</v>
       </c>
       <c r="I2" t="s">
-        <v>4507</v>
+        <v>4506</v>
       </c>
       <c r="J2" t="s">
         <v>4487</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>4529</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>4528</v>
+      </c>
+      <c r="L2" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>146</v>
@@ -15446,12 +15651,15 @@
         <v>4489</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>4530</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>4529</v>
+      </c>
+      <c r="L3" t="s">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>147</v>
@@ -15478,12 +15686,15 @@
         <v>4488</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>4531</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>4530</v>
+      </c>
+      <c r="L4" t="s">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>148</v>
@@ -15507,12 +15718,15 @@
         <v>361</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>4532</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>4531</v>
+      </c>
+      <c r="L5" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>149</v>
@@ -15533,12 +15747,15 @@
         <v>362</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>4533</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>4532</v>
+      </c>
+      <c r="L6" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>150</v>
@@ -15559,12 +15776,15 @@
         <v>363</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>4534</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>4533</v>
+      </c>
+      <c r="L7" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>151</v>
@@ -15579,12 +15799,15 @@
         <v>356</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>4535</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>4534</v>
+      </c>
+      <c r="L8" t="s">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>152</v>
@@ -15599,12 +15822,15 @@
         <v>357</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>4536</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>4535</v>
+      </c>
+      <c r="L9" t="s">
+        <v>4745</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>153</v>
@@ -15619,12 +15845,15 @@
         <v>243</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>4537</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>4536</v>
+      </c>
+      <c r="L10" t="s">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>4463</v>
@@ -15639,12 +15868,15 @@
         <v>251</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>4538</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>4537</v>
+      </c>
+      <c r="L11" t="s">
+        <v>4747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>4464</v>
@@ -15659,12 +15891,15 @@
         <v>262</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>4539</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>4538</v>
+      </c>
+      <c r="L12" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>4465</v>
@@ -15681,10 +15916,13 @@
       <c r="K13" s="10" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
+      <c r="L13" t="s">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>4466</v>
@@ -15699,12 +15937,15 @@
         <v>278</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>4540</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>4539</v>
+      </c>
+      <c r="L14" t="s">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>4467</v>
@@ -15721,10 +15962,13 @@
       <c r="K15" s="10" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
+      <c r="L15" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>4468</v>
@@ -15739,12 +15983,15 @@
         <v>309</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>4541</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>4540</v>
+      </c>
+      <c r="L16" t="s">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>4469</v>
@@ -15756,12 +16003,15 @@
         <v>343</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>4542</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>4541</v>
+      </c>
+      <c r="L17" t="s">
+        <v>4753</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B18" t="s">
         <v>4470</v>
@@ -15773,12 +16023,15 @@
         <v>344</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>4543</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>4542</v>
+      </c>
+      <c r="L18" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="B19" t="s">
         <v>4471</v>
@@ -15792,10 +16045,13 @@
       <c r="K19" s="10" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>40</v>
+      <c r="L19" t="s">
+        <v>4755</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="B20" t="s">
         <v>4472</v>
@@ -15807,12 +16063,15 @@
         <v>346</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>4544</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>4543</v>
+      </c>
+      <c r="L20" t="s">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="B21" t="s">
         <v>4473</v>
@@ -15821,12 +16080,15 @@
         <v>179</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>4545</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>4544</v>
+      </c>
+      <c r="L21" t="s">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="B22" t="s">
         <v>4474</v>
@@ -15835,12 +16097,15 @@
         <v>180</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>4546</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>4545</v>
+      </c>
+      <c r="L22" t="s">
+        <v>4758</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B23" t="s">
         <v>4475</v>
@@ -15849,12 +16114,15 @@
         <v>181</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>4547</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>4546</v>
+      </c>
+      <c r="L23" t="s">
+        <v>4759</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="B24" t="s">
         <v>4476</v>
@@ -15863,12 +16131,15 @@
         <v>182</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>4548</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>4547</v>
+      </c>
+      <c r="L24" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B25" t="s">
         <v>4477</v>
@@ -15877,1188 +16148,1206 @@
         <v>183</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>4549</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>4548</v>
+      </c>
+      <c r="L25" t="s">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>4511</v>
+        <v>4510</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>184</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>4550</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>4549</v>
+      </c>
+      <c r="L26" t="s">
+        <v>4762</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>4512</v>
+        <v>4511</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>185</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>4551</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>4550</v>
+      </c>
+      <c r="L27" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>4513</v>
+        <v>4512</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>186</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>4552</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>4551</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>4514</v>
+        <v>4513</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>187</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>4553</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>4552</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>4515</v>
+        <v>4514</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>188</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>4554</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>4553</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>4516</v>
+        <v>4515</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>189</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>4555</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>52</v>
+        <v>4554</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>4517</v>
+        <v>4516</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>190</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>4556</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>53</v>
+      <c r="A33" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>4518</v>
+        <v>4517</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>191</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>4557</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>54</v>
+      <c r="A34" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>4519</v>
+        <v>4518</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>192</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>4558</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>55</v>
+      <c r="A35" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>4520</v>
+        <v>4519</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>193</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>4559</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>56</v>
+      <c r="A36" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>4521</v>
+        <v>4520</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>194</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>4560</v>
+        <v>4559</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>57</v>
+      <c r="A37" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>4522</v>
+        <v>4521</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>195</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>4561</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>58</v>
+      <c r="A38" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>4523</v>
+        <v>4522</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>196</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>59</v>
+      <c r="A39" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>4524</v>
+        <v>4523</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>197</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>4563</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>60</v>
+      <c r="A40" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>4525</v>
+        <v>4524</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>198</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>4564</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>61</v>
+      <c r="A41" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>4526</v>
+        <v>4525</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>199</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>4565</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>62</v>
+      <c r="A42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>4734</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>200</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>4566</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>63</v>
+      <c r="A43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>4735</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>201</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>4567</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>64</v>
+      <c r="A44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>4736</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>202</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>4568</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>65</v>
+      <c r="A45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>4737</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>203</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>4569</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>66</v>
+      <c r="A46" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>204</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>4570</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>67</v>
+      <c r="A47" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>205</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>4571</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>68</v>
+      <c r="A48" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>206</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>4572</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>69</v>
+      <c r="A49" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>207</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>70</v>
+      <c r="A50" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>208</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>4574</v>
+        <v>4573</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>71</v>
+      <c r="A51" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>209</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>4575</v>
+        <v>4574</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>72</v>
+      <c r="A52" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>210</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>4576</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>73</v>
+      <c r="A53" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>211</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>4577</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>74</v>
+      <c r="A54" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>212</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>4578</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>75</v>
+      <c r="A55" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>213</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>4579</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>76</v>
+      <c r="A56" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>214</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>4580</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>77</v>
+      <c r="A57" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>215</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>4581</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>78</v>
+      <c r="A58" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>216</v>
       </c>
       <c r="K58" s="10" t="s">
-        <v>4582</v>
+        <v>4581</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>79</v>
+      <c r="A59" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>217</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>4583</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>80</v>
+      <c r="A60" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>219</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>4584</v>
+        <v>4583</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>81</v>
+      <c r="A61" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>220</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>4585</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>82</v>
+      <c r="A62" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>221</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>4586</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>83</v>
+      <c r="A63" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>222</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>4587</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>84</v>
+      <c r="A64" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>219</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>4588</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>85</v>
+      <c r="A65" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>220</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>4589</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>86</v>
+      <c r="A66" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>221</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>4590</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>87</v>
+      <c r="A67" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>222</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>4591</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>88</v>
+      <c r="A68" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>223</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>4592</v>
+        <v>4591</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>89</v>
+      <c r="A69" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>224</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>4593</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>90</v>
+      <c r="A70" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>225</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>4594</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>91</v>
+      <c r="A71" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>226</v>
       </c>
       <c r="K71" s="10" t="s">
-        <v>4595</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>92</v>
+      <c r="A72" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>227</v>
       </c>
       <c r="K72" s="10" t="s">
-        <v>4596</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>93</v>
+      <c r="A73" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>228</v>
       </c>
       <c r="K73" s="10" t="s">
-        <v>4597</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>94</v>
+      <c r="A74" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>229</v>
       </c>
       <c r="K74" s="10" t="s">
-        <v>4598</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>95</v>
+      <c r="A75" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>230</v>
       </c>
       <c r="K75" s="10" t="s">
-        <v>4599</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>96</v>
+      <c r="A76" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>231</v>
       </c>
       <c r="K76" s="10" t="s">
-        <v>4600</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>97</v>
+      <c r="A77" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>232</v>
       </c>
       <c r="K77" s="10" t="s">
-        <v>4601</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>98</v>
+      <c r="A78" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>233</v>
       </c>
       <c r="K78" s="10" t="s">
-        <v>4602</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>99</v>
+      <c r="A79" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>234</v>
       </c>
       <c r="K79" s="10" t="s">
-        <v>4603</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>100</v>
+      <c r="A80" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>235</v>
       </c>
       <c r="K80" s="10" t="s">
-        <v>4604</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>101</v>
+      <c r="A81" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>236</v>
       </c>
       <c r="K81" s="10" t="s">
-        <v>4605</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>102</v>
+      <c r="A82" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>237</v>
       </c>
       <c r="K82" s="10" t="s">
-        <v>4606</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>103</v>
+      <c r="A83" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>238</v>
       </c>
       <c r="K83" s="10" t="s">
-        <v>4607</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>104</v>
+      <c r="A84" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>239</v>
       </c>
       <c r="K84" s="10" t="s">
-        <v>4608</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>105</v>
+      <c r="A85" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>240</v>
       </c>
       <c r="K85" s="10" t="s">
-        <v>4609</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>106</v>
+      <c r="A86" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>241</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>4610</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>107</v>
+      <c r="A87" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>242</v>
       </c>
       <c r="K87" s="10" t="s">
-        <v>4611</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>108</v>
+      <c r="A88" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>244</v>
       </c>
       <c r="K88" s="10" t="s">
-        <v>4612</v>
+        <v>4611</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>109</v>
+      <c r="A89" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>245</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>4613</v>
+        <v>4612</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>110</v>
+      <c r="A90" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>246</v>
       </c>
       <c r="K90" s="10" t="s">
-        <v>4614</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>111</v>
+      <c r="A91" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>247</v>
       </c>
       <c r="K91" s="10" t="s">
-        <v>4615</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>112</v>
+      <c r="A92" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>248</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>4616</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>113</v>
+      <c r="A93" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>249</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>4617</v>
+        <v>4616</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>114</v>
+      <c r="A94" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>250</v>
       </c>
       <c r="K94" s="10" t="s">
-        <v>4618</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>115</v>
+      <c r="A95" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>252</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>4619</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>116</v>
+      <c r="A96" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>253</v>
       </c>
       <c r="K96" s="10" t="s">
-        <v>4620</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>117</v>
+      <c r="A97" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>254</v>
       </c>
       <c r="K97" s="10" t="s">
-        <v>4621</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>118</v>
+      <c r="A98" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>255</v>
       </c>
       <c r="K98" s="10" t="s">
-        <v>4622</v>
+        <v>4621</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>119</v>
+      <c r="A99" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>256</v>
       </c>
       <c r="K99" s="10" t="s">
-        <v>4623</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>120</v>
+      <c r="A100" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>257</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>4624</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>121</v>
+      <c r="A101" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>258</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>4625</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>122</v>
+      <c r="A102" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>259</v>
       </c>
       <c r="K102" s="10" t="s">
-        <v>4626</v>
+        <v>4625</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>123</v>
+      <c r="A103" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>260</v>
       </c>
       <c r="K103" s="10" t="s">
-        <v>4627</v>
+        <v>4626</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>124</v>
+      <c r="A104" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>261</v>
       </c>
       <c r="K104" s="10" t="s">
-        <v>4628</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>125</v>
+      <c r="A105" s="2" t="s">
+        <v>4507</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>263</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>4629</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>4508</v>
+      <c r="A106" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>264</v>
       </c>
       <c r="K106" s="10" t="s">
-        <v>4630</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>127</v>
+      <c r="A107" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>265</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>4631</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
-        <v>126</v>
+      <c r="A108" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>266</v>
       </c>
       <c r="K108" s="10" t="s">
-        <v>4632</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>128</v>
+      <c r="A109" s="2" t="s">
+        <v>4508</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>267</v>
       </c>
       <c r="K109" s="10" t="s">
-        <v>4633</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="1" t="s">
         <v>4509</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>268</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>4634</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>4510</v>
+      <c r="A111" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>269</v>
       </c>
       <c r="K111" s="10" t="s">
-        <v>4635</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>129</v>
+      <c r="A112" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="D112" s="10" t="s">
         <v>271</v>
       </c>
       <c r="K112" s="10" t="s">
-        <v>4636</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>130</v>
+      <c r="A113" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>272</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>4637</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
-        <v>131</v>
+      <c r="A114" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>273</v>
       </c>
       <c r="K114" s="10" t="s">
-        <v>4638</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>132</v>
+      <c r="A115" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>274</v>
       </c>
       <c r="K115" s="10" t="s">
-        <v>4639</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>133</v>
+      <c r="A116" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>275</v>
       </c>
       <c r="K116" s="10" t="s">
-        <v>4640</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>134</v>
+      <c r="A117" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>276</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>4641</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>135</v>
+      <c r="A118" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>277</v>
       </c>
       <c r="K118" s="10" t="s">
-        <v>4642</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>136</v>
+      <c r="A119" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>279</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>4643</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
-        <v>137</v>
+      <c r="A120" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>280</v>
       </c>
       <c r="K120" s="10" t="s">
-        <v>4644</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>138</v>
+      <c r="A121" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>281</v>
       </c>
       <c r="K121" s="10" t="s">
-        <v>4645</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
-        <v>139</v>
+      <c r="A122" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>282</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>4646</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>140</v>
+      <c r="A123" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>283</v>
       </c>
       <c r="K123" s="10" t="s">
-        <v>4647</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
-        <v>141</v>
+      <c r="A124" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>285</v>
       </c>
       <c r="K124" s="10" t="s">
-        <v>4648</v>
+        <v>4647</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>142</v>
+      <c r="A125" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="D125" s="10" t="s">
         <v>286</v>
       </c>
       <c r="K125" s="10" t="s">
-        <v>4649</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
-        <v>143</v>
+      <c r="A126" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>287</v>
       </c>
       <c r="K126" s="10" t="s">
-        <v>4650</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>144</v>
+      <c r="A127" t="s">
+        <v>145</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>288</v>
       </c>
       <c r="K127" s="10" t="s">
-        <v>4651</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>145</v>
-      </c>
       <c r="D128" s="10" t="s">
         <v>289</v>
       </c>
       <c r="K128" s="10" t="s">
-        <v>4652</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="129" spans="4:11" x14ac:dyDescent="0.25">
@@ -17066,7 +17355,7 @@
         <v>290</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>4636</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="130" spans="4:11" x14ac:dyDescent="0.25">
@@ -17074,7 +17363,7 @@
         <v>291</v>
       </c>
       <c r="K130" s="10" t="s">
-        <v>4653</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="131" spans="4:11" x14ac:dyDescent="0.25">
@@ -17082,7 +17371,7 @@
         <v>292</v>
       </c>
       <c r="K131" s="10" t="s">
-        <v>4654</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="132" spans="4:11" x14ac:dyDescent="0.25">
@@ -17090,7 +17379,7 @@
         <v>293</v>
       </c>
       <c r="K132" s="10" t="s">
-        <v>4655</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="133" spans="4:11" x14ac:dyDescent="0.25">
@@ -17098,7 +17387,7 @@
         <v>294</v>
       </c>
       <c r="K133" s="10" t="s">
-        <v>4656</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="134" spans="4:11" x14ac:dyDescent="0.25">
@@ -17106,7 +17395,7 @@
         <v>295</v>
       </c>
       <c r="K134" s="10" t="s">
-        <v>4657</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="135" spans="4:11" x14ac:dyDescent="0.25">
@@ -17114,7 +17403,7 @@
         <v>296</v>
       </c>
       <c r="K135" s="10" t="s">
-        <v>4658</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="136" spans="4:11" x14ac:dyDescent="0.25">
@@ -17122,7 +17411,7 @@
         <v>297</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>4659</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="137" spans="4:11" x14ac:dyDescent="0.25">
@@ -17130,7 +17419,7 @@
         <v>298</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>4660</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="138" spans="4:11" x14ac:dyDescent="0.25">
@@ -17138,7 +17427,7 @@
         <v>299</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>4661</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="139" spans="4:11" x14ac:dyDescent="0.25">
@@ -17146,7 +17435,7 @@
         <v>300</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>4662</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="140" spans="4:11" x14ac:dyDescent="0.25">
@@ -17154,7 +17443,7 @@
         <v>301</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>4663</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="141" spans="4:11" x14ac:dyDescent="0.25">
@@ -17162,7 +17451,7 @@
         <v>302</v>
       </c>
       <c r="K141" s="10" t="s">
-        <v>4664</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="142" spans="4:11" x14ac:dyDescent="0.25">
@@ -17170,7 +17459,7 @@
         <v>303</v>
       </c>
       <c r="K142" s="10" t="s">
-        <v>4665</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="143" spans="4:11" x14ac:dyDescent="0.25">
@@ -17178,7 +17467,7 @@
         <v>304</v>
       </c>
       <c r="K143" s="10" t="s">
-        <v>4666</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="144" spans="4:11" x14ac:dyDescent="0.25">
@@ -17186,7 +17475,7 @@
         <v>305</v>
       </c>
       <c r="K144" s="10" t="s">
-        <v>4667</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="145" spans="4:11" x14ac:dyDescent="0.25">
@@ -17194,7 +17483,7 @@
         <v>306</v>
       </c>
       <c r="K145" s="10" t="s">
-        <v>4668</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="146" spans="4:11" x14ac:dyDescent="0.25">
@@ -17202,7 +17491,7 @@
         <v>307</v>
       </c>
       <c r="K146" s="10" t="s">
-        <v>4669</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="147" spans="4:11" x14ac:dyDescent="0.25">
@@ -17210,7 +17499,7 @@
         <v>308</v>
       </c>
       <c r="K147" s="10" t="s">
-        <v>4670</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="148" spans="4:11" x14ac:dyDescent="0.25">
@@ -17218,7 +17507,7 @@
         <v>310</v>
       </c>
       <c r="K148" s="10" t="s">
-        <v>4671</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="149" spans="4:11" x14ac:dyDescent="0.25">
@@ -17226,7 +17515,7 @@
         <v>311</v>
       </c>
       <c r="K149" s="10" t="s">
-        <v>4672</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="150" spans="4:11" x14ac:dyDescent="0.25">
@@ -17234,7 +17523,7 @@
         <v>312</v>
       </c>
       <c r="K150" s="10" t="s">
-        <v>4673</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="151" spans="4:11" x14ac:dyDescent="0.25">
@@ -17242,7 +17531,7 @@
         <v>313</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>4674</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="152" spans="4:11" x14ac:dyDescent="0.25">
@@ -17250,7 +17539,7 @@
         <v>314</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>4675</v>
+        <v>4674</v>
       </c>
     </row>
     <row r="153" spans="4:11" x14ac:dyDescent="0.25">
@@ -17258,7 +17547,7 @@
         <v>315</v>
       </c>
       <c r="K153" s="10" t="s">
-        <v>4676</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="154" spans="4:11" x14ac:dyDescent="0.25">
@@ -17266,7 +17555,7 @@
         <v>316</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>4677</v>
+        <v>4676</v>
       </c>
     </row>
     <row r="155" spans="4:11" x14ac:dyDescent="0.25">
@@ -17274,7 +17563,7 @@
         <v>317</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>4678</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="156" spans="4:11" x14ac:dyDescent="0.25">
@@ -17282,7 +17571,7 @@
         <v>318</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>4679</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="157" spans="4:11" x14ac:dyDescent="0.25">
@@ -17290,7 +17579,7 @@
         <v>319</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>4680</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="158" spans="4:11" x14ac:dyDescent="0.25">
@@ -17298,7 +17587,7 @@
         <v>320</v>
       </c>
       <c r="K158" s="10" t="s">
-        <v>4681</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="159" spans="4:11" x14ac:dyDescent="0.25">
@@ -17306,7 +17595,7 @@
         <v>321</v>
       </c>
       <c r="K159" s="10" t="s">
-        <v>4682</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="160" spans="4:11" x14ac:dyDescent="0.25">
@@ -17314,7 +17603,7 @@
         <v>322</v>
       </c>
       <c r="K160" s="10" t="s">
-        <v>4683</v>
+        <v>4682</v>
       </c>
     </row>
     <row r="161" spans="4:11" x14ac:dyDescent="0.25">
@@ -17322,7 +17611,7 @@
         <v>323</v>
       </c>
       <c r="K161" s="10" t="s">
-        <v>4684</v>
+        <v>4683</v>
       </c>
     </row>
     <row r="162" spans="4:11" x14ac:dyDescent="0.25">
@@ -17330,7 +17619,7 @@
         <v>324</v>
       </c>
       <c r="K162" s="10" t="s">
-        <v>4685</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="163" spans="4:11" x14ac:dyDescent="0.25">
@@ -17338,7 +17627,7 @@
         <v>325</v>
       </c>
       <c r="K163" s="10" t="s">
-        <v>4686</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="164" spans="4:11" x14ac:dyDescent="0.25">
@@ -17346,7 +17635,7 @@
         <v>326</v>
       </c>
       <c r="K164" s="10" t="s">
-        <v>4687</v>
+        <v>4686</v>
       </c>
     </row>
     <row r="165" spans="4:11" x14ac:dyDescent="0.25">
@@ -17354,281 +17643,281 @@
         <v>327</v>
       </c>
       <c r="K165" s="10" t="s">
-        <v>4688</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="166" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D166" s="10" t="s">
-        <v>4505</v>
+        <v>4504</v>
       </c>
       <c r="K166" s="10" t="s">
-        <v>4689</v>
+        <v>4688</v>
       </c>
     </row>
     <row r="167" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D167" s="10" t="s">
-        <v>4527</v>
+        <v>4526</v>
       </c>
       <c r="K167" s="10" t="s">
-        <v>4690</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="168" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D168" s="10"/>
       <c r="K168" s="10" t="s">
-        <v>4691</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="169" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D169" s="10"/>
       <c r="K169" s="10" t="s">
-        <v>4692</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="170" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D170" s="10"/>
       <c r="K170" s="10" t="s">
-        <v>4693</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="171" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D171" s="10"/>
       <c r="K171" s="10" t="s">
-        <v>4694</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="172" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D172" s="10"/>
       <c r="K172" s="10" t="s">
-        <v>4695</v>
+        <v>4694</v>
       </c>
     </row>
     <row r="173" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D173" s="10"/>
       <c r="K173" s="10" t="s">
-        <v>4696</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="174" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D174" s="10"/>
       <c r="K174" s="10" t="s">
-        <v>4697</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="175" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D175" s="10"/>
       <c r="K175" s="10" t="s">
-        <v>4698</v>
+        <v>4697</v>
       </c>
     </row>
     <row r="176" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D176" s="10"/>
       <c r="K176" s="10" t="s">
-        <v>4699</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="177" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D177" s="10"/>
       <c r="K177" s="10" t="s">
-        <v>4700</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="178" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D178" s="10"/>
       <c r="K178" s="10" t="s">
-        <v>4701</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="179" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D179" s="10"/>
       <c r="K179" s="10" t="s">
-        <v>4702</v>
+        <v>4701</v>
       </c>
     </row>
     <row r="180" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D180" s="10"/>
       <c r="K180" s="10" t="s">
-        <v>4703</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="181" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D181" s="10"/>
       <c r="K181" s="10" t="s">
-        <v>4704</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="182" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D182" s="10"/>
       <c r="K182" s="10" t="s">
-        <v>4705</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="183" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D183" s="10"/>
       <c r="K183" s="10" t="s">
-        <v>4706</v>
+        <v>4705</v>
       </c>
     </row>
     <row r="184" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D184" s="10"/>
       <c r="K184" s="10" t="s">
-        <v>4707</v>
+        <v>4706</v>
       </c>
     </row>
     <row r="185" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D185" s="10"/>
       <c r="K185" s="10" t="s">
-        <v>4708</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="186" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D186" s="10"/>
       <c r="K186" s="10" t="s">
-        <v>4709</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="187" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D187" s="10"/>
       <c r="K187" s="10" t="s">
-        <v>4710</v>
+        <v>4709</v>
       </c>
     </row>
     <row r="188" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D188" s="10"/>
       <c r="K188" s="10" t="s">
-        <v>4711</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="189" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D189" s="10"/>
       <c r="K189" s="10" t="s">
-        <v>4712</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="190" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D190" s="10"/>
       <c r="K190" s="10" t="s">
-        <v>4713</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="191" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D191" s="10"/>
       <c r="K191" s="10" t="s">
-        <v>4714</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="192" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D192" s="10"/>
       <c r="K192" s="10" t="s">
-        <v>4715</v>
+        <v>4714</v>
       </c>
     </row>
     <row r="193" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D193" s="10"/>
       <c r="K193" s="10" t="s">
-        <v>4716</v>
+        <v>4715</v>
       </c>
     </row>
     <row r="194" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D194" s="10"/>
       <c r="K194" s="10" t="s">
-        <v>4717</v>
+        <v>4716</v>
       </c>
     </row>
     <row r="195" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D195" s="10"/>
       <c r="K195" s="10" t="s">
-        <v>4718</v>
+        <v>4717</v>
       </c>
     </row>
     <row r="196" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D196" s="10"/>
       <c r="K196" s="10" t="s">
-        <v>4719</v>
+        <v>4718</v>
       </c>
     </row>
     <row r="197" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D197" s="10"/>
       <c r="K197" s="10" t="s">
-        <v>4720</v>
+        <v>4719</v>
       </c>
     </row>
     <row r="198" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D198" s="10"/>
       <c r="K198" s="10" t="s">
-        <v>4721</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="199" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D199" s="10"/>
       <c r="K199" s="10" t="s">
-        <v>4722</v>
+        <v>4721</v>
       </c>
     </row>
     <row r="200" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D200" s="10"/>
       <c r="K200" s="10" t="s">
-        <v>4723</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="201" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D201" s="10"/>
       <c r="K201" s="10" t="s">
-        <v>4724</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="202" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D202" s="10"/>
       <c r="K202" s="10" t="s">
-        <v>4725</v>
+        <v>4724</v>
       </c>
     </row>
     <row r="203" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D203" s="10"/>
       <c r="K203" s="10" t="s">
-        <v>4726</v>
+        <v>4725</v>
       </c>
     </row>
     <row r="204" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D204" s="10"/>
       <c r="K204" s="10" t="s">
-        <v>4727</v>
+        <v>4726</v>
       </c>
     </row>
     <row r="205" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D205" s="10"/>
       <c r="K205" s="10" t="s">
-        <v>4728</v>
+        <v>4727</v>
       </c>
     </row>
     <row r="206" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D206" s="10"/>
       <c r="K206" s="10" t="s">
-        <v>4729</v>
+        <v>4728</v>
       </c>
     </row>
     <row r="207" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D207" s="10"/>
       <c r="K207" s="10" t="s">
-        <v>4730</v>
+        <v>4729</v>
       </c>
     </row>
     <row r="208" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D208" s="10"/>
       <c r="K208" s="10" t="s">
-        <v>4731</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="209" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D209" s="10"/>
       <c r="K209" s="10" t="s">
-        <v>4732</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="210" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D210" s="10"/>
       <c r="K210" s="10" t="s">
-        <v>4733</v>
+        <v>4732</v>
       </c>
     </row>
     <row r="211" spans="4:11" x14ac:dyDescent="0.25">
@@ -41146,11 +41435,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6089D82B-CC96-4176-9A54-02325BF7F952}">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -41162,11 +41451,11 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>4504</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>159</v>
+      <c r="A2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>4734</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -41174,7 +41463,7 @@
         <v>126</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>146</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -41182,7 +41471,7 @@
         <v>126</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>147</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -41190,119 +41479,119 @@
         <v>126</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>148</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>149</v>
+      <c r="B6" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>150</v>
+        <v>4734</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>151</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>159</v>
+        <v>127</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>4736</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>152</v>
+        <v>127</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>4769</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>153</v>
+        <v>127</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>159</v>
+      <c r="B12" s="24" t="s">
+        <v>4734</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>4735</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>150</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>147</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>149</v>
+        <v>139</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>4734</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>152</v>
+      <c r="B18" s="24" t="s">
+        <v>4736</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>153</v>
+      <c r="B19" s="24" t="s">
+        <v>4737</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -41315,26 +41604,26 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>4463</v>
+        <v>28</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>4770</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>4464</v>
+        <v>28</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>4465</v>
+      <c r="B23" s="6" t="s">
+        <v>4463</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -41342,7 +41631,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>4466</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -41350,7 +41639,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>4467</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -41358,7 +41647,7 @@
         <v>29</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>4468</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -41366,71 +41655,71 @@
         <v>29</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>4469</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>159</v>
+      <c r="B28" s="10" t="s">
+        <v>4468</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>4470</v>
+        <v>29</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>4469</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>4471</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>4472</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>4771</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>4473</v>
+        <v>30</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>4474</v>
+      <c r="B33" s="6" t="s">
+        <v>4470</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>4475</v>
+      <c r="B34" s="6" t="s">
+        <v>4471</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>4476</v>
+      <c r="B35" s="6" t="s">
+        <v>4472</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -41438,47 +41727,47 @@
         <v>115</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>4477</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>159</v>
+      <c r="B37" s="10" t="s">
+        <v>4474</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>4470</v>
+        <v>115</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>4475</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>4471</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>4472</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>4473</v>
+        <v>115</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -41486,7 +41775,7 @@
         <v>116</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>4474</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -41494,7 +41783,7 @@
         <v>116</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>4475</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -41502,7 +41791,7 @@
         <v>116</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>4476</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -41510,150 +41799,214 @@
         <v>116</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>4477</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="10" t="s">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B47" s="24" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>4510</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>4511</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B48" s="24" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>4512</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B49" s="24" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B54" s="10" t="s">
         <v>4513</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B50" s="24" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B55" s="10" t="s">
         <v>4514</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B51" s="24" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>4515</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B52" s="24" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>4516</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B53" s="24" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>4517</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B54" s="24" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>4518</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B55" s="24" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>4519</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B56" s="24" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>4520</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B57" s="24" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B62" s="10" t="s">
         <v>4521</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B58" s="24" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B63" s="10" t="s">
         <v>4522</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B59" s="24" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B64" s="10" t="s">
         <v>4523</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B60" s="24" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B65" s="10" t="s">
         <v>4524</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B61" s="24" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>4525</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="24" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>4526</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="22" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B63" s="25" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="23" t="s">
         <v>159</v>
       </c>
     </row>
@@ -41666,8 +42019,789 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7909F7-AFFF-4DF2-95A8-3867BFD28EC6}">
+  <dimension ref="A1:C70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" style="26" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>4737</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>4745</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>4747</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>4753</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>4755</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>4758</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>4759</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>4762</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>4745</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>4747</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>4753</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>4755</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>4758</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>4759</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>4762</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>4764</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>4765</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>4766</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>4767</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>4734</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>4768</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="27"/>
+      <c r="B70" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5D69-D337-4E34-A409-23B0595B8838}">
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -41815,7 +42949,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>4494</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -42148,431 +43282,431 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>219</v>
+      <c r="A64" s="10" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>4526</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
-        <v>4527</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>4527</v>
+      <c r="A68" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>266</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>267</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>268</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>269</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>4502</v>
@@ -42580,7 +43714,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>4502</v>
@@ -42588,7 +43722,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>4502</v>
@@ -42596,7 +43730,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>4502</v>
@@ -42604,7 +43738,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>4502</v>
@@ -42612,7 +43746,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>4502</v>
@@ -42620,7 +43754,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>4502</v>
@@ -42628,7 +43762,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>4502</v>
@@ -42636,39 +43770,39 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>4502</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>4502</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>4502</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>4502</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>4503</v>
@@ -42676,7 +43810,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>4503</v>
@@ -42684,7 +43818,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>4503</v>
@@ -42692,7 +43826,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>4503</v>
@@ -42700,7 +43834,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>4503</v>
@@ -42708,7 +43842,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>4503</v>
@@ -42716,7 +43850,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>4503</v>
@@ -42724,7 +43858,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>4503</v>
@@ -42732,7 +43866,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>4503</v>
@@ -42740,7 +43874,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>4503</v>
@@ -42748,7 +43882,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>4503</v>
@@ -42756,7 +43890,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>4503</v>
@@ -42764,7 +43898,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>4503</v>
@@ -42772,7 +43906,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>4503</v>
@@ -42780,7 +43914,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>4503</v>
@@ -42788,7 +43922,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>4503</v>
@@ -42796,7 +43930,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>4503</v>
@@ -42804,7 +43938,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>4503</v>
@@ -42812,7 +43946,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>4503</v>
@@ -42820,186 +43954,154 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>4503</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>4503</v>
+        <v>311</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>4503</v>
+        <v>312</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>4503</v>
+        <v>313</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="22" t="s">
+      <c r="A162" s="22" t="s">
+        <v>4504</v>
+      </c>
+      <c r="B162" s="10" t="s">
         <v>4505</v>
-      </c>
-      <c r="B166" s="10" t="s">
-        <v>4506</v>
       </c>
     </row>
   </sheetData>
@@ -43010,7 +44112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A6A1FE-F544-4336-8056-3A04420364F9}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -43068,13 +44170,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F92CC8-C507-429E-80E1-05934A71C4A2}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -43090,7 +44192,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>4735</v>
+        <v>4773</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -43098,7 +44200,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>4734</v>
+        <v>4733</v>
       </c>
     </row>
   </sheetData>

--- a/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
+++ b/IfcManager.BL/Files/IfcManagerFiles/IFC parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supi\source\repos\IfcManager\IfcManager.BL\Files\IfcManagerFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBE4F34-879F-4479-A536-5A8175BFA926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC98564-5D3F-4B7D-B434-F6294D5ADF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22140" yWindow="2910" windowWidth="38700" windowHeight="15345" tabRatio="720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="885" windowWidth="10785" windowHeight="12585" tabRatio="720" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="4774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7711" uniqueCount="4773">
   <si>
     <t>Data Type</t>
   </si>
@@ -13488,9 +13488,6 @@
     <t>Function</t>
   </si>
   <si>
-    <t>DelimetedByDotFirstPart</t>
-  </si>
-  <si>
     <t>PropertySet_3L_Identity</t>
   </si>
   <si>
@@ -13515,12 +13512,6 @@
     <t>Safety</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>SetTrueIfSourceEqualsTo</t>
-  </si>
-  <si>
     <t>EAR_EARTHWORKS</t>
   </si>
   <si>
@@ -14365,6 +14356,12 @@
   </si>
   <si>
     <t>&lt;ConstructionPhase&gt;.&lt;LocationRoot&gt;.&lt;SubLocation&gt;.&lt;OrientationID&gt;.&lt;4DGroup&gt;.&lt;WorkStep&gt;</t>
+  </si>
+  <si>
+    <t>.Split('.')[0]</t>
+  </si>
+  <si>
+    <t>==TMP</t>
   </si>
 </sst>
 </file>
@@ -14655,7 +14652,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
@@ -14705,6 +14702,7 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14717,7 +14715,7 @@
     <cellStyle name="Normal 4 3" xfId="8" xr:uid="{647E405E-89F1-46B3-9D0F-7CADBB992D37}"/>
     <cellStyle name="Normal 5" xfId="4" xr:uid="{6DF54FAE-2483-4EEF-8D6C-A9E4680CE2F0}"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
     <dxf>
       <font>
         <b val="0"/>
@@ -14767,57 +14765,28 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.79998168889431442"/>
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -14920,6 +14889,59 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -14946,7 +14968,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:L211" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}" name="Table1" displayName="Table1" ref="A1:L211" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A1:L211" xr:uid="{C8250F1A-5710-4EF4-AF6C-E853327E9515}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{7CD8FD0B-335F-4B2A-AB69-8C9EE375AC9F}" name="LocationRoot"/>
@@ -14967,50 +14989,49 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B71" totalsRowShown="0" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}" name="Table3" displayName="Table3" ref="A1:B71" totalsRowShown="0" tableBorderDxfId="10">
   <autoFilter ref="A1:B71" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="11" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{4911EFDD-6DC1-4E8E-B65F-3B23EC4A6795}" name="LocationRoot" dataDxfId="9" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{4C9A0A65-1DCA-4EF9-BCD3-256BA43BE659}" name="SubLocation" dataDxfId="8" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{05794BD0-36D1-4902-97E0-542EBA653550}" name="Table8" displayName="Table8" ref="A1:C69" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{05794BD0-36D1-4902-97E0-542EBA653550}" name="Table8" displayName="Table8" ref="A1:C69" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:C69" xr:uid="{05794BD0-36D1-4902-97E0-542EBA653550}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C69">
     <sortCondition ref="A1:A69"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{809AE534-87F1-493B-8DE3-D1EF41305073}" name="LocationRoot" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{8AEA72EF-D1C3-4C17-ACDD-D668C0F1C361}" name="SubLocation" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{8522D775-A8DF-46ED-B8DF-932C6B351FDB}" name="SpaceID" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{809AE534-87F1-493B-8DE3-D1EF41305073}" name="LocationRoot" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{8AEA72EF-D1C3-4C17-ACDD-D668C0F1C361}" name="SubLocation" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{8522D775-A8DF-46ED-B8DF-932C6B351FDB}" name="SpaceID" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B162" totalsRowShown="0" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{34C8FE38-B078-4F8C-9774-DDAA2832123B}" name="Table37" displayName="Table37" ref="A1:B162" totalsRowShown="0" tableBorderDxfId="14">
   <autoFilter ref="A1:B162" xr:uid="{61158B8F-257E-4C05-AF7E-1081BDB1D7D4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{A51CE557-8403-4E9D-AE1D-40B894898E7E}" name="TypeID" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{798C78D9-BEA0-4284-A401-798B0EA1ECE7}" name="4DGroup" dataDxfId="12" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}" name="Table4" displayName="Table4" ref="A1:D3" totalsRowShown="0">
-  <autoFilter ref="A1:D3" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A0CDC16A-3706-47C9-9E77-C6678E0326C3}" name="Source Property Name" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{4BC30CBE-C5F5-4A85-8E76-B531F3265739}" name="Target Property Name" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{DF1EFB03-B9BD-43A3-A819-4FC3E2BCCDD0}" name="Function"/>
-    <tableColumn id="4" xr3:uid="{F590C646-6614-44AA-8C48-74C4100AC227}" name="Value"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}" name="Table4" displayName="Table4" ref="A1:C3" totalsRowShown="0">
+  <autoFilter ref="A1:C3" xr:uid="{B0F2E238-E1C5-400D-B944-80181B90F609}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A0CDC16A-3706-47C9-9E77-C6678E0326C3}" name="Source Property Name" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{40BECBAF-51FC-4594-AD7E-85C1A4F98169}" name="Function" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{4BC30CBE-C5F5-4A85-8E76-B531F3265739}" name="Target Property Name" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15312,7 +15333,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -15323,7 +15344,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -15334,7 +15355,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -15345,7 +15366,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -15356,7 +15377,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -15367,7 +15388,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -15378,7 +15399,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -15389,7 +15410,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -15400,7 +15421,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -15411,10 +15432,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="B11" t="s">
-        <v>4527</v>
+        <v>4524</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -15422,7 +15443,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -15433,10 +15454,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>4482</v>
+      </c>
+      <c r="B13" t="s">
         <v>4483</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4484</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -15444,7 +15465,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -15455,7 +15476,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -15466,7 +15487,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
@@ -15477,7 +15498,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -15488,7 +15509,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -15499,7 +15520,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
@@ -15510,7 +15531,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
@@ -15578,7 +15599,7 @@
         <v>22</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>4527</v>
+        <v>4524</v>
       </c>
       <c r="L1" s="18" t="s">
         <v>11</v>
@@ -15610,16 +15631,16 @@
         <v>358</v>
       </c>
       <c r="I2" t="s">
-        <v>4506</v>
+        <v>4503</v>
       </c>
       <c r="J2" t="s">
-        <v>4487</v>
+        <v>4486</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>4528</v>
+        <v>4525</v>
       </c>
       <c r="L2" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -15648,13 +15669,13 @@
         <v>359</v>
       </c>
       <c r="J3" t="s">
-        <v>4489</v>
+        <v>4488</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>4529</v>
+        <v>4526</v>
       </c>
       <c r="L3" t="s">
-        <v>4739</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -15683,13 +15704,13 @@
         <v>360</v>
       </c>
       <c r="J4" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>4530</v>
+        <v>4527</v>
       </c>
       <c r="L4" t="s">
-        <v>4740</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -15718,10 +15739,10 @@
         <v>361</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>4531</v>
+        <v>4528</v>
       </c>
       <c r="L5" t="s">
-        <v>4741</v>
+        <v>4738</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -15747,10 +15768,10 @@
         <v>362</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>4532</v>
+        <v>4529</v>
       </c>
       <c r="L6" t="s">
-        <v>4742</v>
+        <v>4739</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -15776,10 +15797,10 @@
         <v>363</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>4533</v>
+        <v>4530</v>
       </c>
       <c r="L7" t="s">
-        <v>4743</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -15799,10 +15820,10 @@
         <v>356</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>4534</v>
+        <v>4531</v>
       </c>
       <c r="L8" t="s">
-        <v>4744</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -15822,10 +15843,10 @@
         <v>357</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>4535</v>
+        <v>4532</v>
       </c>
       <c r="L9" t="s">
-        <v>4745</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -15845,10 +15866,10 @@
         <v>243</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>4536</v>
+        <v>4533</v>
       </c>
       <c r="L10" t="s">
-        <v>4746</v>
+        <v>4743</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -15868,10 +15889,10 @@
         <v>251</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>4537</v>
+        <v>4534</v>
       </c>
       <c r="L11" t="s">
-        <v>4747</v>
+        <v>4744</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -15891,10 +15912,10 @@
         <v>262</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>4538</v>
+        <v>4535</v>
       </c>
       <c r="L12" t="s">
-        <v>4748</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -15917,7 +15938,7 @@
         <v>336</v>
       </c>
       <c r="L13" t="s">
-        <v>4749</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -15937,10 +15958,10 @@
         <v>278</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>4539</v>
+        <v>4536</v>
       </c>
       <c r="L14" t="s">
-        <v>4750</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -15963,7 +15984,7 @@
         <v>360</v>
       </c>
       <c r="L15" t="s">
-        <v>4751</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -15983,10 +16004,10 @@
         <v>309</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>4540</v>
+        <v>4537</v>
       </c>
       <c r="L16" t="s">
-        <v>4752</v>
+        <v>4749</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -16003,10 +16024,10 @@
         <v>343</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>4541</v>
+        <v>4538</v>
       </c>
       <c r="L17" t="s">
-        <v>4753</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -16023,10 +16044,10 @@
         <v>344</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>4542</v>
+        <v>4539</v>
       </c>
       <c r="L18" t="s">
-        <v>4754</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -16046,7 +16067,7 @@
         <v>345</v>
       </c>
       <c r="L19" t="s">
-        <v>4755</v>
+        <v>4752</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -16063,10 +16084,10 @@
         <v>346</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>4543</v>
+        <v>4540</v>
       </c>
       <c r="L20" t="s">
-        <v>4756</v>
+        <v>4753</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -16080,10 +16101,10 @@
         <v>179</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>4544</v>
+        <v>4541</v>
       </c>
       <c r="L21" t="s">
-        <v>4757</v>
+        <v>4754</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -16097,10 +16118,10 @@
         <v>180</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>4545</v>
+        <v>4542</v>
       </c>
       <c r="L22" t="s">
-        <v>4758</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -16114,10 +16135,10 @@
         <v>181</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>4546</v>
+        <v>4543</v>
       </c>
       <c r="L23" t="s">
-        <v>4759</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -16131,10 +16152,10 @@
         <v>182</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>4547</v>
+        <v>4544</v>
       </c>
       <c r="L24" t="s">
-        <v>4760</v>
+        <v>4757</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -16148,10 +16169,10 @@
         <v>183</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>4548</v>
+        <v>4545</v>
       </c>
       <c r="L25" t="s">
-        <v>4761</v>
+        <v>4758</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -16159,16 +16180,16 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>4510</v>
+        <v>4507</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>184</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>4549</v>
+        <v>4546</v>
       </c>
       <c r="L26" t="s">
-        <v>4762</v>
+        <v>4759</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -16176,16 +16197,16 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>4511</v>
+        <v>4508</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>185</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>4550</v>
+        <v>4547</v>
       </c>
       <c r="L27" t="s">
-        <v>4763</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -16193,13 +16214,13 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>4512</v>
+        <v>4509</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>186</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>4551</v>
+        <v>4548</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -16207,13 +16228,13 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>4513</v>
+        <v>4510</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>187</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>4552</v>
+        <v>4549</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -16221,13 +16242,13 @@
         <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>4514</v>
+        <v>4511</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>188</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>4553</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -16235,13 +16256,13 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>4515</v>
+        <v>4512</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>189</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>4554</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -16249,13 +16270,13 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>4516</v>
+        <v>4513</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>190</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>4555</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -16263,13 +16284,13 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>4517</v>
+        <v>4514</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>191</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>4556</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -16277,13 +16298,13 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>4518</v>
+        <v>4515</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>192</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>4557</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -16291,13 +16312,13 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>4519</v>
+        <v>4516</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>193</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>4558</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -16305,13 +16326,13 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>4520</v>
+        <v>4517</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>194</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>4559</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -16319,13 +16340,13 @@
         <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>4521</v>
+        <v>4518</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>195</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>4560</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -16333,13 +16354,13 @@
         <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>4522</v>
+        <v>4519</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>196</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>4561</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -16347,13 +16368,13 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>4523</v>
+        <v>4520</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>197</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>4562</v>
+        <v>4559</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -16361,13 +16382,13 @@
         <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>4524</v>
+        <v>4521</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>198</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>4563</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -16375,13 +16396,13 @@
         <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>4525</v>
+        <v>4522</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>199</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>4564</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -16389,13 +16410,13 @@
         <v>63</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>200</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>4565</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -16403,13 +16424,13 @@
         <v>64</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>4735</v>
+        <v>4732</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>201</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>4566</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -16417,13 +16438,13 @@
         <v>65</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>202</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>4567</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -16431,13 +16452,13 @@
         <v>66</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>4737</v>
+        <v>4734</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>203</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>4568</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -16448,7 +16469,7 @@
         <v>204</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>4569</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -16459,7 +16480,7 @@
         <v>205</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>4570</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -16470,7 +16491,7 @@
         <v>206</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>4571</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -16481,7 +16502,7 @@
         <v>207</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>4572</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -16492,7 +16513,7 @@
         <v>208</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>4573</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -16503,7 +16524,7 @@
         <v>209</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>4574</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -16514,7 +16535,7 @@
         <v>210</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>4575</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -16525,7 +16546,7 @@
         <v>211</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>4576</v>
+        <v>4573</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -16536,7 +16557,7 @@
         <v>212</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>4577</v>
+        <v>4574</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -16547,7 +16568,7 @@
         <v>213</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>4578</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -16558,7 +16579,7 @@
         <v>214</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>4579</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -16569,7 +16590,7 @@
         <v>215</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>4580</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -16580,7 +16601,7 @@
         <v>216</v>
       </c>
       <c r="K58" s="10" t="s">
-        <v>4581</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -16591,7 +16612,7 @@
         <v>217</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>4582</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -16602,7 +16623,7 @@
         <v>219</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>4583</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -16613,7 +16634,7 @@
         <v>220</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>4584</v>
+        <v>4581</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -16624,7 +16645,7 @@
         <v>221</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>4585</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -16635,7 +16656,7 @@
         <v>222</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>4586</v>
+        <v>4583</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -16646,7 +16667,7 @@
         <v>219</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>4587</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -16657,7 +16678,7 @@
         <v>220</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>4588</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -16668,7 +16689,7 @@
         <v>221</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>4589</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -16679,7 +16700,7 @@
         <v>222</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>4590</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -16690,7 +16711,7 @@
         <v>223</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>4591</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -16701,7 +16722,7 @@
         <v>224</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>4592</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -16712,7 +16733,7 @@
         <v>225</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>4593</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -16723,7 +16744,7 @@
         <v>226</v>
       </c>
       <c r="K71" s="10" t="s">
-        <v>4594</v>
+        <v>4591</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -16734,7 +16755,7 @@
         <v>227</v>
       </c>
       <c r="K72" s="10" t="s">
-        <v>4595</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -16745,7 +16766,7 @@
         <v>228</v>
       </c>
       <c r="K73" s="10" t="s">
-        <v>4596</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -16756,7 +16777,7 @@
         <v>229</v>
       </c>
       <c r="K74" s="10" t="s">
-        <v>4597</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -16767,7 +16788,7 @@
         <v>230</v>
       </c>
       <c r="K75" s="10" t="s">
-        <v>4598</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -16778,7 +16799,7 @@
         <v>231</v>
       </c>
       <c r="K76" s="10" t="s">
-        <v>4599</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -16789,7 +16810,7 @@
         <v>232</v>
       </c>
       <c r="K77" s="10" t="s">
-        <v>4600</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -16800,7 +16821,7 @@
         <v>233</v>
       </c>
       <c r="K78" s="10" t="s">
-        <v>4601</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -16811,7 +16832,7 @@
         <v>234</v>
       </c>
       <c r="K79" s="10" t="s">
-        <v>4602</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -16822,7 +16843,7 @@
         <v>235</v>
       </c>
       <c r="K80" s="10" t="s">
-        <v>4603</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -16833,7 +16854,7 @@
         <v>236</v>
       </c>
       <c r="K81" s="10" t="s">
-        <v>4604</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -16844,7 +16865,7 @@
         <v>237</v>
       </c>
       <c r="K82" s="10" t="s">
-        <v>4605</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -16855,7 +16876,7 @@
         <v>238</v>
       </c>
       <c r="K83" s="10" t="s">
-        <v>4606</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -16866,7 +16887,7 @@
         <v>239</v>
       </c>
       <c r="K84" s="10" t="s">
-        <v>4607</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -16877,7 +16898,7 @@
         <v>240</v>
       </c>
       <c r="K85" s="10" t="s">
-        <v>4608</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -16888,7 +16909,7 @@
         <v>241</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>4609</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -16899,7 +16920,7 @@
         <v>242</v>
       </c>
       <c r="K87" s="10" t="s">
-        <v>4610</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -16910,7 +16931,7 @@
         <v>244</v>
       </c>
       <c r="K88" s="10" t="s">
-        <v>4611</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -16921,7 +16942,7 @@
         <v>245</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>4612</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -16932,7 +16953,7 @@
         <v>246</v>
       </c>
       <c r="K90" s="10" t="s">
-        <v>4613</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -16943,7 +16964,7 @@
         <v>247</v>
       </c>
       <c r="K91" s="10" t="s">
-        <v>4614</v>
+        <v>4611</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -16954,7 +16975,7 @@
         <v>248</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>4615</v>
+        <v>4612</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -16965,7 +16986,7 @@
         <v>249</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>4616</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -16976,7 +16997,7 @@
         <v>250</v>
       </c>
       <c r="K94" s="10" t="s">
-        <v>4617</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -16987,7 +17008,7 @@
         <v>252</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>4618</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -16998,7 +17019,7 @@
         <v>253</v>
       </c>
       <c r="K96" s="10" t="s">
-        <v>4619</v>
+        <v>4616</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -17009,7 +17030,7 @@
         <v>254</v>
       </c>
       <c r="K97" s="10" t="s">
-        <v>4620</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -17020,7 +17041,7 @@
         <v>255</v>
       </c>
       <c r="K98" s="10" t="s">
-        <v>4621</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -17031,7 +17052,7 @@
         <v>256</v>
       </c>
       <c r="K99" s="10" t="s">
-        <v>4622</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -17042,7 +17063,7 @@
         <v>257</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>4623</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -17053,7 +17074,7 @@
         <v>258</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>4624</v>
+        <v>4621</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -17064,7 +17085,7 @@
         <v>259</v>
       </c>
       <c r="K102" s="10" t="s">
-        <v>4625</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -17075,7 +17096,7 @@
         <v>260</v>
       </c>
       <c r="K103" s="10" t="s">
-        <v>4626</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -17086,18 +17107,18 @@
         <v>261</v>
       </c>
       <c r="K104" s="10" t="s">
-        <v>4627</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>263</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>4628</v>
+        <v>4625</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -17108,7 +17129,7 @@
         <v>264</v>
       </c>
       <c r="K106" s="10" t="s">
-        <v>4629</v>
+        <v>4626</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -17119,7 +17140,7 @@
         <v>265</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>4630</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -17130,29 +17151,29 @@
         <v>266</v>
       </c>
       <c r="K108" s="10" t="s">
-        <v>4631</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>4508</v>
+        <v>4505</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>267</v>
       </c>
       <c r="K109" s="10" t="s">
-        <v>4632</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>4509</v>
+        <v>4506</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>268</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>4633</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -17163,7 +17184,7 @@
         <v>269</v>
       </c>
       <c r="K111" s="10" t="s">
-        <v>4634</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -17174,7 +17195,7 @@
         <v>271</v>
       </c>
       <c r="K112" s="10" t="s">
-        <v>4635</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -17185,7 +17206,7 @@
         <v>272</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>4636</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -17196,7 +17217,7 @@
         <v>273</v>
       </c>
       <c r="K114" s="10" t="s">
-        <v>4637</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -17207,7 +17228,7 @@
         <v>274</v>
       </c>
       <c r="K115" s="10" t="s">
-        <v>4638</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -17218,7 +17239,7 @@
         <v>275</v>
       </c>
       <c r="K116" s="10" t="s">
-        <v>4639</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -17229,7 +17250,7 @@
         <v>276</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>4640</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -17240,7 +17261,7 @@
         <v>277</v>
       </c>
       <c r="K118" s="10" t="s">
-        <v>4641</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -17251,7 +17272,7 @@
         <v>279</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>4642</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -17262,7 +17283,7 @@
         <v>280</v>
       </c>
       <c r="K120" s="10" t="s">
-        <v>4643</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -17273,7 +17294,7 @@
         <v>281</v>
       </c>
       <c r="K121" s="10" t="s">
-        <v>4644</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -17284,7 +17305,7 @@
         <v>282</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>4645</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -17295,7 +17316,7 @@
         <v>283</v>
       </c>
       <c r="K123" s="10" t="s">
-        <v>4646</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -17306,7 +17327,7 @@
         <v>285</v>
       </c>
       <c r="K124" s="10" t="s">
-        <v>4647</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -17317,7 +17338,7 @@
         <v>286</v>
       </c>
       <c r="K125" s="10" t="s">
-        <v>4648</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -17328,7 +17349,7 @@
         <v>287</v>
       </c>
       <c r="K126" s="10" t="s">
-        <v>4649</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -17339,7 +17360,7 @@
         <v>288</v>
       </c>
       <c r="K127" s="10" t="s">
-        <v>4650</v>
+        <v>4647</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -17347,7 +17368,7 @@
         <v>289</v>
       </c>
       <c r="K128" s="10" t="s">
-        <v>4651</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="129" spans="4:11" x14ac:dyDescent="0.25">
@@ -17355,7 +17376,7 @@
         <v>290</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>4635</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="130" spans="4:11" x14ac:dyDescent="0.25">
@@ -17363,7 +17384,7 @@
         <v>291</v>
       </c>
       <c r="K130" s="10" t="s">
-        <v>4652</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="131" spans="4:11" x14ac:dyDescent="0.25">
@@ -17371,7 +17392,7 @@
         <v>292</v>
       </c>
       <c r="K131" s="10" t="s">
-        <v>4653</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="132" spans="4:11" x14ac:dyDescent="0.25">
@@ -17379,7 +17400,7 @@
         <v>293</v>
       </c>
       <c r="K132" s="10" t="s">
-        <v>4654</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="133" spans="4:11" x14ac:dyDescent="0.25">
@@ -17387,7 +17408,7 @@
         <v>294</v>
       </c>
       <c r="K133" s="10" t="s">
-        <v>4655</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="134" spans="4:11" x14ac:dyDescent="0.25">
@@ -17395,7 +17416,7 @@
         <v>295</v>
       </c>
       <c r="K134" s="10" t="s">
-        <v>4656</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="135" spans="4:11" x14ac:dyDescent="0.25">
@@ -17403,7 +17424,7 @@
         <v>296</v>
       </c>
       <c r="K135" s="10" t="s">
-        <v>4657</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="136" spans="4:11" x14ac:dyDescent="0.25">
@@ -17411,7 +17432,7 @@
         <v>297</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>4658</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="137" spans="4:11" x14ac:dyDescent="0.25">
@@ -17419,7 +17440,7 @@
         <v>298</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>4659</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="138" spans="4:11" x14ac:dyDescent="0.25">
@@ -17427,7 +17448,7 @@
         <v>299</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>4660</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="139" spans="4:11" x14ac:dyDescent="0.25">
@@ -17435,7 +17456,7 @@
         <v>300</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>4661</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="140" spans="4:11" x14ac:dyDescent="0.25">
@@ -17443,7 +17464,7 @@
         <v>301</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>4662</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="141" spans="4:11" x14ac:dyDescent="0.25">
@@ -17451,7 +17472,7 @@
         <v>302</v>
       </c>
       <c r="K141" s="10" t="s">
-        <v>4663</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="142" spans="4:11" x14ac:dyDescent="0.25">
@@ -17459,7 +17480,7 @@
         <v>303</v>
       </c>
       <c r="K142" s="10" t="s">
-        <v>4664</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="143" spans="4:11" x14ac:dyDescent="0.25">
@@ -17467,7 +17488,7 @@
         <v>304</v>
       </c>
       <c r="K143" s="10" t="s">
-        <v>4665</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="144" spans="4:11" x14ac:dyDescent="0.25">
@@ -17475,7 +17496,7 @@
         <v>305</v>
       </c>
       <c r="K144" s="10" t="s">
-        <v>4666</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="145" spans="4:11" x14ac:dyDescent="0.25">
@@ -17483,7 +17504,7 @@
         <v>306</v>
       </c>
       <c r="K145" s="10" t="s">
-        <v>4667</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="146" spans="4:11" x14ac:dyDescent="0.25">
@@ -17491,7 +17512,7 @@
         <v>307</v>
       </c>
       <c r="K146" s="10" t="s">
-        <v>4668</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="147" spans="4:11" x14ac:dyDescent="0.25">
@@ -17499,7 +17520,7 @@
         <v>308</v>
       </c>
       <c r="K147" s="10" t="s">
-        <v>4669</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="148" spans="4:11" x14ac:dyDescent="0.25">
@@ -17507,7 +17528,7 @@
         <v>310</v>
       </c>
       <c r="K148" s="10" t="s">
-        <v>4670</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="149" spans="4:11" x14ac:dyDescent="0.25">
@@ -17515,7 +17536,7 @@
         <v>311</v>
       </c>
       <c r="K149" s="10" t="s">
-        <v>4671</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="150" spans="4:11" x14ac:dyDescent="0.25">
@@ -17523,7 +17544,7 @@
         <v>312</v>
       </c>
       <c r="K150" s="10" t="s">
-        <v>4672</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="151" spans="4:11" x14ac:dyDescent="0.25">
@@ -17531,7 +17552,7 @@
         <v>313</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>4673</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="152" spans="4:11" x14ac:dyDescent="0.25">
@@ -17539,7 +17560,7 @@
         <v>314</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>4674</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="153" spans="4:11" x14ac:dyDescent="0.25">
@@ -17547,7 +17568,7 @@
         <v>315</v>
       </c>
       <c r="K153" s="10" t="s">
-        <v>4675</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="154" spans="4:11" x14ac:dyDescent="0.25">
@@ -17555,7 +17576,7 @@
         <v>316</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>4676</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="155" spans="4:11" x14ac:dyDescent="0.25">
@@ -17563,7 +17584,7 @@
         <v>317</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>4677</v>
+        <v>4674</v>
       </c>
     </row>
     <row r="156" spans="4:11" x14ac:dyDescent="0.25">
@@ -17571,7 +17592,7 @@
         <v>318</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>4678</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="157" spans="4:11" x14ac:dyDescent="0.25">
@@ -17579,7 +17600,7 @@
         <v>319</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>4679</v>
+        <v>4676</v>
       </c>
     </row>
     <row r="158" spans="4:11" x14ac:dyDescent="0.25">
@@ -17587,7 +17608,7 @@
         <v>320</v>
       </c>
       <c r="K158" s="10" t="s">
-        <v>4680</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="159" spans="4:11" x14ac:dyDescent="0.25">
@@ -17595,7 +17616,7 @@
         <v>321</v>
       </c>
       <c r="K159" s="10" t="s">
-        <v>4681</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="160" spans="4:11" x14ac:dyDescent="0.25">
@@ -17603,7 +17624,7 @@
         <v>322</v>
       </c>
       <c r="K160" s="10" t="s">
-        <v>4682</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="161" spans="4:11" x14ac:dyDescent="0.25">
@@ -17611,7 +17632,7 @@
         <v>323</v>
       </c>
       <c r="K161" s="10" t="s">
-        <v>4683</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="162" spans="4:11" x14ac:dyDescent="0.25">
@@ -17619,7 +17640,7 @@
         <v>324</v>
       </c>
       <c r="K162" s="10" t="s">
-        <v>4684</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="163" spans="4:11" x14ac:dyDescent="0.25">
@@ -17627,7 +17648,7 @@
         <v>325</v>
       </c>
       <c r="K163" s="10" t="s">
-        <v>4685</v>
+        <v>4682</v>
       </c>
     </row>
     <row r="164" spans="4:11" x14ac:dyDescent="0.25">
@@ -17635,7 +17656,7 @@
         <v>326</v>
       </c>
       <c r="K164" s="10" t="s">
-        <v>4686</v>
+        <v>4683</v>
       </c>
     </row>
     <row r="165" spans="4:11" x14ac:dyDescent="0.25">
@@ -17643,281 +17664,281 @@
         <v>327</v>
       </c>
       <c r="K165" s="10" t="s">
-        <v>4687</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="166" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D166" s="10" t="s">
-        <v>4504</v>
+        <v>4501</v>
       </c>
       <c r="K166" s="10" t="s">
-        <v>4688</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="167" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D167" s="10" t="s">
-        <v>4526</v>
+        <v>4523</v>
       </c>
       <c r="K167" s="10" t="s">
-        <v>4689</v>
+        <v>4686</v>
       </c>
     </row>
     <row r="168" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D168" s="10"/>
       <c r="K168" s="10" t="s">
-        <v>4690</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="169" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D169" s="10"/>
       <c r="K169" s="10" t="s">
-        <v>4691</v>
+        <v>4688</v>
       </c>
     </row>
     <row r="170" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D170" s="10"/>
       <c r="K170" s="10" t="s">
-        <v>4692</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="171" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D171" s="10"/>
       <c r="K171" s="10" t="s">
-        <v>4693</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="172" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D172" s="10"/>
       <c r="K172" s="10" t="s">
-        <v>4694</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="173" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D173" s="10"/>
       <c r="K173" s="10" t="s">
-        <v>4695</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="174" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D174" s="10"/>
       <c r="K174" s="10" t="s">
-        <v>4696</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="175" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D175" s="10"/>
       <c r="K175" s="10" t="s">
-        <v>4697</v>
+        <v>4694</v>
       </c>
     </row>
     <row r="176" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D176" s="10"/>
       <c r="K176" s="10" t="s">
-        <v>4698</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="177" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D177" s="10"/>
       <c r="K177" s="10" t="s">
-        <v>4699</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="178" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D178" s="10"/>
       <c r="K178" s="10" t="s">
-        <v>4700</v>
+        <v>4697</v>
       </c>
     </row>
     <row r="179" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D179" s="10"/>
       <c r="K179" s="10" t="s">
-        <v>4701</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="180" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D180" s="10"/>
       <c r="K180" s="10" t="s">
-        <v>4702</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="181" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D181" s="10"/>
       <c r="K181" s="10" t="s">
-        <v>4703</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="182" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D182" s="10"/>
       <c r="K182" s="10" t="s">
-        <v>4704</v>
+        <v>4701</v>
       </c>
     </row>
     <row r="183" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D183" s="10"/>
       <c r="K183" s="10" t="s">
-        <v>4705</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="184" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D184" s="10"/>
       <c r="K184" s="10" t="s">
-        <v>4706</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="185" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D185" s="10"/>
       <c r="K185" s="10" t="s">
-        <v>4707</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="186" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D186" s="10"/>
       <c r="K186" s="10" t="s">
-        <v>4708</v>
+        <v>4705</v>
       </c>
     </row>
     <row r="187" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D187" s="10"/>
       <c r="K187" s="10" t="s">
-        <v>4709</v>
+        <v>4706</v>
       </c>
     </row>
     <row r="188" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D188" s="10"/>
       <c r="K188" s="10" t="s">
-        <v>4710</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="189" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D189" s="10"/>
       <c r="K189" s="10" t="s">
-        <v>4711</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="190" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D190" s="10"/>
       <c r="K190" s="10" t="s">
-        <v>4712</v>
+        <v>4709</v>
       </c>
     </row>
     <row r="191" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D191" s="10"/>
       <c r="K191" s="10" t="s">
-        <v>4713</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="192" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D192" s="10"/>
       <c r="K192" s="10" t="s">
-        <v>4714</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="193" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D193" s="10"/>
       <c r="K193" s="10" t="s">
-        <v>4715</v>
+        <v>4712</v>
       </c>
     </row>
     <row r="194" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D194" s="10"/>
       <c r="K194" s="10" t="s">
-        <v>4716</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="195" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D195" s="10"/>
       <c r="K195" s="10" t="s">
-        <v>4717</v>
+        <v>4714</v>
       </c>
     </row>
     <row r="196" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D196" s="10"/>
       <c r="K196" s="10" t="s">
-        <v>4718</v>
+        <v>4715</v>
       </c>
     </row>
     <row r="197" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D197" s="10"/>
       <c r="K197" s="10" t="s">
-        <v>4719</v>
+        <v>4716</v>
       </c>
     </row>
     <row r="198" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D198" s="10"/>
       <c r="K198" s="10" t="s">
-        <v>4720</v>
+        <v>4717</v>
       </c>
     </row>
     <row r="199" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D199" s="10"/>
       <c r="K199" s="10" t="s">
-        <v>4721</v>
+        <v>4718</v>
       </c>
     </row>
     <row r="200" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D200" s="10"/>
       <c r="K200" s="10" t="s">
-        <v>4722</v>
+        <v>4719</v>
       </c>
     </row>
     <row r="201" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D201" s="10"/>
       <c r="K201" s="10" t="s">
-        <v>4723</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="202" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D202" s="10"/>
       <c r="K202" s="10" t="s">
-        <v>4724</v>
+        <v>4721</v>
       </c>
     </row>
     <row r="203" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D203" s="10"/>
       <c r="K203" s="10" t="s">
-        <v>4725</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="204" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D204" s="10"/>
       <c r="K204" s="10" t="s">
-        <v>4726</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="205" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D205" s="10"/>
       <c r="K205" s="10" t="s">
-        <v>4727</v>
+        <v>4724</v>
       </c>
     </row>
     <row r="206" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D206" s="10"/>
       <c r="K206" s="10" t="s">
-        <v>4728</v>
+        <v>4725</v>
       </c>
     </row>
     <row r="207" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D207" s="10"/>
       <c r="K207" s="10" t="s">
-        <v>4729</v>
+        <v>4726</v>
       </c>
     </row>
     <row r="208" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D208" s="10"/>
       <c r="K208" s="10" t="s">
-        <v>4730</v>
+        <v>4727</v>
       </c>
     </row>
     <row r="209" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D209" s="10"/>
       <c r="K209" s="10" t="s">
-        <v>4731</v>
+        <v>4728</v>
       </c>
     </row>
     <row r="210" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D210" s="10"/>
       <c r="K210" s="10" t="s">
-        <v>4732</v>
+        <v>4729</v>
       </c>
     </row>
     <row r="211" spans="4:11" x14ac:dyDescent="0.25">
@@ -41455,7 +41476,7 @@
         <v>126</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -41463,7 +41484,7 @@
         <v>126</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>4735</v>
+        <v>4732</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -41471,7 +41492,7 @@
         <v>126</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -41479,7 +41500,7 @@
         <v>126</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>4769</v>
+        <v>4766</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -41495,7 +41516,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -41503,7 +41524,7 @@
         <v>127</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>4735</v>
+        <v>4732</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -41511,7 +41532,7 @@
         <v>127</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -41519,7 +41540,7 @@
         <v>127</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>4769</v>
+        <v>4766</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -41535,7 +41556,7 @@
         <v>140</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -41543,7 +41564,7 @@
         <v>140</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>4735</v>
+        <v>4732</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -41551,7 +41572,7 @@
         <v>140</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -41559,7 +41580,7 @@
         <v>140</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>4737</v>
+        <v>4734</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -41575,7 +41596,7 @@
         <v>139</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -41583,7 +41604,7 @@
         <v>139</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -41591,7 +41612,7 @@
         <v>139</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>4737</v>
+        <v>4734</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -41607,7 +41628,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>4770</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -41687,7 +41708,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>4771</v>
+        <v>4768</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -41844,135 +41865,135 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
+        <v>4504</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>4507</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>4510</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>4511</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>4512</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>4513</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>4514</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>4515</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>4516</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>4517</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>4518</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>4519</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>4520</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>4521</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>4522</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>4523</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>4524</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>4525</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>4507</v>
+        <v>4504</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>159</v>
@@ -41983,7 +42004,7 @@
         <v>131</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>4772</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -41999,7 +42020,7 @@
         <v>132</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>4772</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -42044,10 +42065,10 @@
         <v>139</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -42055,10 +42076,10 @@
         <v>139</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -42066,10 +42087,10 @@
         <v>139</v>
       </c>
       <c r="B4" s="25" t="s">
+        <v>4733</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>4736</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>4739</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -42077,10 +42098,10 @@
         <v>139</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>4737</v>
+        <v>4734</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -42088,10 +42109,10 @@
         <v>140</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -42099,10 +42120,10 @@
         <v>127</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -42110,10 +42131,10 @@
         <v>127</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>4739</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -42121,10 +42142,10 @@
         <v>127</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>4740</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -42132,10 +42153,10 @@
         <v>127</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>4741</v>
+        <v>4738</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -42143,10 +42164,10 @@
         <v>127</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>4742</v>
+        <v>4739</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -42154,10 +42175,10 @@
         <v>127</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>4743</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -42165,10 +42186,10 @@
         <v>127</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>4744</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -42176,10 +42197,10 @@
         <v>127</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>4745</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -42187,10 +42208,10 @@
         <v>127</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>4746</v>
+        <v>4743</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -42198,10 +42219,10 @@
         <v>127</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>4747</v>
+        <v>4744</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -42209,10 +42230,10 @@
         <v>127</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>4748</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -42220,10 +42241,10 @@
         <v>127</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>4749</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -42231,10 +42252,10 @@
         <v>127</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>4750</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -42242,10 +42263,10 @@
         <v>127</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>4751</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -42253,10 +42274,10 @@
         <v>127</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>4752</v>
+        <v>4749</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -42264,10 +42285,10 @@
         <v>127</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>4753</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -42275,10 +42296,10 @@
         <v>127</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>4754</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -42286,10 +42307,10 @@
         <v>127</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>4755</v>
+        <v>4752</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -42297,10 +42318,10 @@
         <v>127</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>4756</v>
+        <v>4753</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -42308,10 +42329,10 @@
         <v>127</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>4757</v>
+        <v>4754</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -42319,10 +42340,10 @@
         <v>127</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>4758</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -42330,10 +42351,10 @@
         <v>127</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>4759</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -42341,10 +42362,10 @@
         <v>127</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>4760</v>
+        <v>4757</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -42352,10 +42373,10 @@
         <v>127</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>4761</v>
+        <v>4758</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -42363,10 +42384,10 @@
         <v>127</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>4762</v>
+        <v>4759</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -42374,10 +42395,10 @@
         <v>127</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>4763</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -42385,10 +42406,10 @@
         <v>127</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -42396,10 +42417,10 @@
         <v>127</v>
       </c>
       <c r="B34" s="25" t="s">
+        <v>4733</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>4736</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>4739</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -42407,10 +42428,10 @@
         <v>127</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>4740</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -42418,10 +42439,10 @@
         <v>127</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>4741</v>
+        <v>4738</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -42429,10 +42450,10 @@
         <v>127</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>4742</v>
+        <v>4739</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -42440,10 +42461,10 @@
         <v>127</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>4743</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -42451,10 +42472,10 @@
         <v>126</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -42462,10 +42483,10 @@
         <v>126</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>4739</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -42473,10 +42494,10 @@
         <v>126</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>4740</v>
+        <v>4737</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -42484,10 +42505,10 @@
         <v>126</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>4741</v>
+        <v>4738</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -42495,10 +42516,10 @@
         <v>126</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>4742</v>
+        <v>4739</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -42506,10 +42527,10 @@
         <v>126</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>4743</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -42517,10 +42538,10 @@
         <v>126</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>4744</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -42528,10 +42549,10 @@
         <v>126</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>4745</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -42539,10 +42560,10 @@
         <v>126</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>4746</v>
+        <v>4743</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -42550,10 +42571,10 @@
         <v>126</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>4747</v>
+        <v>4744</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -42561,10 +42582,10 @@
         <v>126</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>4748</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -42572,10 +42593,10 @@
         <v>126</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>4749</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -42583,10 +42604,10 @@
         <v>126</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>4750</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -42594,10 +42615,10 @@
         <v>126</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>4751</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -42605,10 +42626,10 @@
         <v>126</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>4752</v>
+        <v>4749</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -42616,10 +42637,10 @@
         <v>126</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>4753</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -42627,10 +42648,10 @@
         <v>126</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>4754</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -42638,10 +42659,10 @@
         <v>126</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>4755</v>
+        <v>4752</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -42649,10 +42670,10 @@
         <v>126</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>4756</v>
+        <v>4753</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -42660,10 +42681,10 @@
         <v>126</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>4757</v>
+        <v>4754</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -42671,10 +42692,10 @@
         <v>126</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>4758</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -42682,10 +42703,10 @@
         <v>126</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>4759</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -42693,10 +42714,10 @@
         <v>126</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>4760</v>
+        <v>4757</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -42704,10 +42725,10 @@
         <v>126</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>4761</v>
+        <v>4758</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -42715,10 +42736,10 @@
         <v>126</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>4762</v>
+        <v>4759</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -42726,10 +42747,10 @@
         <v>126</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>4763</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -42737,10 +42758,10 @@
         <v>126</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>4764</v>
+        <v>4761</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -42748,10 +42769,10 @@
         <v>126</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>4765</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -42759,10 +42780,10 @@
         <v>126</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>4766</v>
+        <v>4763</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -42770,10 +42791,10 @@
         <v>126</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>4767</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -42781,10 +42802,10 @@
         <v>126</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>4768</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -42813,7 +42834,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>4484</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -42821,7 +42842,7 @@
         <v>160</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -42829,7 +42850,7 @@
         <v>161</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -42837,7 +42858,7 @@
         <v>162</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -42845,7 +42866,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -42853,7 +42874,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -42861,7 +42882,7 @@
         <v>165</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -42869,7 +42890,7 @@
         <v>166</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -42877,7 +42898,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -42885,7 +42906,7 @@
         <v>168</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -42893,7 +42914,7 @@
         <v>169</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -42901,7 +42922,7 @@
         <v>170</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>4492</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -42909,7 +42930,7 @@
         <v>171</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>4493</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -42917,7 +42938,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>4494</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -42925,7 +42946,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>4493</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -42933,7 +42954,7 @@
         <v>174</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>4494</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -42941,7 +42962,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>4494</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -42949,7 +42970,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -42957,7 +42978,7 @@
         <v>177</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -42965,7 +42986,7 @@
         <v>178</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -42973,7 +42994,7 @@
         <v>179</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>4493</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -42981,7 +43002,7 @@
         <v>180</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -42989,7 +43010,7 @@
         <v>181</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -42997,7 +43018,7 @@
         <v>182</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -43005,7 +43026,7 @@
         <v>183</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>4494</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -43013,7 +43034,7 @@
         <v>184</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -43021,7 +43042,7 @@
         <v>185</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -43029,7 +43050,7 @@
         <v>186</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -43037,7 +43058,7 @@
         <v>187</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>4495</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -43077,7 +43098,7 @@
         <v>192</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>4496</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -43101,7 +43122,7 @@
         <v>195</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>4497</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -43109,7 +43130,7 @@
         <v>196</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>4497</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -43117,7 +43138,7 @@
         <v>197</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>4498</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -43125,7 +43146,7 @@
         <v>198</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>4498</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -43133,7 +43154,7 @@
         <v>199</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>4498</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -43141,7 +43162,7 @@
         <v>200</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>4498</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -43149,7 +43170,7 @@
         <v>201</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>4499</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -43157,7 +43178,7 @@
         <v>202</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>4500</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -43165,7 +43186,7 @@
         <v>203</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>4500</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -43173,7 +43194,7 @@
         <v>204</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -43181,7 +43202,7 @@
         <v>205</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -43189,7 +43210,7 @@
         <v>206</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -43197,7 +43218,7 @@
         <v>207</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -43205,7 +43226,7 @@
         <v>208</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -43213,7 +43234,7 @@
         <v>209</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -43221,7 +43242,7 @@
         <v>210</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -43229,7 +43250,7 @@
         <v>211</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -43237,7 +43258,7 @@
         <v>212</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -43245,7 +43266,7 @@
         <v>213</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -43253,7 +43274,7 @@
         <v>214</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -43261,7 +43282,7 @@
         <v>215</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -43269,7 +43290,7 @@
         <v>216</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -43277,7 +43298,7 @@
         <v>217</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>4501</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -43314,10 +43335,10 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>4526</v>
+        <v>4523</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>4526</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -43677,7 +43698,7 @@
         <v>271</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -43685,7 +43706,7 @@
         <v>272</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -43693,7 +43714,7 @@
         <v>273</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -43701,7 +43722,7 @@
         <v>274</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -43709,7 +43730,7 @@
         <v>275</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -43717,7 +43738,7 @@
         <v>276</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -43725,7 +43746,7 @@
         <v>277</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -43733,7 +43754,7 @@
         <v>279</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -43741,7 +43762,7 @@
         <v>280</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -43749,7 +43770,7 @@
         <v>281</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -43757,7 +43778,7 @@
         <v>282</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -43765,7 +43786,7 @@
         <v>283</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>4502</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -43773,7 +43794,7 @@
         <v>285</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -43781,7 +43802,7 @@
         <v>286</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -43789,7 +43810,7 @@
         <v>287</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -43797,7 +43818,7 @@
         <v>288</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -43805,7 +43826,7 @@
         <v>289</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -43813,7 +43834,7 @@
         <v>290</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -43821,7 +43842,7 @@
         <v>291</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -43829,7 +43850,7 @@
         <v>292</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -43837,7 +43858,7 @@
         <v>293</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -43845,7 +43866,7 @@
         <v>294</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -43853,7 +43874,7 @@
         <v>295</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -43861,7 +43882,7 @@
         <v>296</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -43869,7 +43890,7 @@
         <v>297</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -43877,7 +43898,7 @@
         <v>298</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -43885,7 +43906,7 @@
         <v>299</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -43893,7 +43914,7 @@
         <v>300</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -43901,7 +43922,7 @@
         <v>301</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -43909,7 +43930,7 @@
         <v>302</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -43917,7 +43938,7 @@
         <v>303</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -43925,7 +43946,7 @@
         <v>304</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -43933,7 +43954,7 @@
         <v>306</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -43941,7 +43962,7 @@
         <v>307</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -43949,7 +43970,7 @@
         <v>308</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>4503</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -44098,10 +44119,10 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="22" t="s">
-        <v>4504</v>
+        <v>4501</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>4505</v>
+        <v>4502</v>
       </c>
     </row>
   </sheetData>
@@ -44114,52 +44135,44 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A6A1FE-F544-4336-8056-3A04420364F9}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4479</v>
       </c>
       <c r="B1" t="s">
+        <v>4480</v>
+      </c>
+      <c r="C1" t="s">
         <v>4478</v>
       </c>
-      <c r="C1" t="s">
-        <v>4480</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4490</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="31" t="s">
+        <v>4771</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>4481</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="31" t="s">
+        <v>4772</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4491</v>
-      </c>
-      <c r="D3" t="s">
-        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -44181,10 +44194,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4484</v>
+      </c>
+      <c r="B1" t="s">
         <v>4485</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4486</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -44192,7 +44205,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>4773</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -44200,7 +44213,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>4733</v>
+        <v>4730</v>
       </c>
     </row>
   </sheetData>
